--- a/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>CRH</t>
   </si>
@@ -763,7 +763,7 @@
         <v>16136000</v>
       </c>
       <c r="E8" s="3">
-        <v>17725000</v>
+        <v>32723000</v>
       </c>
       <c r="F8" s="3">
         <v>14998000</v>
@@ -825,7 +825,7 @@
         <v>10855000</v>
       </c>
       <c r="E9" s="3">
-        <v>11601000</v>
+        <v>21908000</v>
       </c>
       <c r="F9" s="3">
         <v>10243000</v>
@@ -887,7 +887,7 @@
         <v>5281000</v>
       </c>
       <c r="E10" s="3">
-        <v>6124000</v>
+        <v>10815000</v>
       </c>
       <c r="F10" s="3">
         <v>4755000</v>
@@ -1093,14 +1093,14 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>35000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4000</v>
       </c>
       <c r="G14" s="3">
         <v>12000</v>
@@ -1242,7 +1242,7 @@
         <v>14509000</v>
       </c>
       <c r="E17" s="3">
-        <v>15216000</v>
+        <v>28914000</v>
       </c>
       <c r="F17" s="3">
         <v>13613000</v>
@@ -1304,7 +1304,7 @@
         <v>1627000</v>
       </c>
       <c r="E18" s="3">
-        <v>2509000</v>
+        <v>3809000</v>
       </c>
       <c r="F18" s="3">
         <v>1385000</v>
@@ -1390,7 +1390,7 @@
         <v>-117000</v>
       </c>
       <c r="E20" s="3">
-        <v>-243000</v>
+        <v>-348000</v>
       </c>
       <c r="F20" s="3">
         <v>-182000</v>
@@ -1452,7 +1452,7 @@
         <v>2403000</v>
       </c>
       <c r="E21" s="3">
-        <v>3162000</v>
+        <v>5218000</v>
       </c>
       <c r="F21" s="3">
         <v>2064000</v>
@@ -1576,7 +1576,7 @@
         <v>1510000</v>
       </c>
       <c r="E23" s="3">
-        <v>2266000</v>
+        <v>3461000</v>
       </c>
       <c r="F23" s="3">
         <v>1203000</v>
@@ -1638,7 +1638,7 @@
         <v>332000</v>
       </c>
       <c r="E24" s="3">
-        <v>520000</v>
+        <v>762000</v>
       </c>
       <c r="F24" s="3">
         <v>265000</v>
@@ -1762,7 +1762,7 @@
         <v>1178000</v>
       </c>
       <c r="E26" s="3">
-        <v>1746000</v>
+        <v>2699000</v>
       </c>
       <c r="F26" s="3">
         <v>938000</v>
@@ -1824,7 +1824,7 @@
         <v>1168000</v>
       </c>
       <c r="E27" s="3">
-        <v>1731000</v>
+        <v>2672000</v>
       </c>
       <c r="F27" s="3">
         <v>926000</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>22000</v>
+        <v>1190000</v>
       </c>
       <c r="F29" s="3">
         <v>1168000</v>
@@ -2134,7 +2134,7 @@
         <v>117000</v>
       </c>
       <c r="E32" s="3">
-        <v>243000</v>
+        <v>348000</v>
       </c>
       <c r="F32" s="3">
         <v>182000</v>
@@ -2196,7 +2196,7 @@
         <v>1168000</v>
       </c>
       <c r="E33" s="3">
-        <v>1753000</v>
+        <v>3862000</v>
       </c>
       <c r="F33" s="3">
         <v>2094000</v>
@@ -2320,7 +2320,7 @@
         <v>1168000</v>
       </c>
       <c r="E35" s="3">
-        <v>1753000</v>
+        <v>3862000</v>
       </c>
       <c r="F35" s="3">
         <v>2094000</v>
@@ -2621,7 +2621,7 @@
         <v>6450000</v>
       </c>
       <c r="E43" s="3">
-        <v>4632000</v>
+        <v>4363000</v>
       </c>
       <c r="F43" s="3">
         <v>5858000</v>
@@ -2745,7 +2745,7 @@
         <v>8000</v>
       </c>
       <c r="E45" s="3">
-        <v>39000</v>
+        <v>442000</v>
       </c>
       <c r="F45" s="3">
         <v>112000</v>
@@ -2807,7 +2807,7 @@
         <v>15009000</v>
       </c>
       <c r="E46" s="3">
-        <v>14801000</v>
+        <v>14833000</v>
       </c>
       <c r="F46" s="3">
         <v>16588000</v>
@@ -2931,7 +2931,7 @@
         <v>19322000</v>
       </c>
       <c r="E48" s="3">
-        <v>18921000</v>
+        <v>36606000</v>
       </c>
       <c r="F48" s="3">
         <v>18298000</v>
@@ -2993,7 +2993,7 @@
         <v>10399000</v>
       </c>
       <c r="E49" s="3">
-        <v>10287000</v>
+        <v>20574000</v>
       </c>
       <c r="F49" s="3">
         <v>8726000</v>
@@ -3179,7 +3179,7 @@
         <v>368000</v>
       </c>
       <c r="E52" s="3">
-        <v>352000</v>
+        <v>959000</v>
       </c>
       <c r="F52" s="3">
         <v>345000</v>
@@ -3303,7 +3303,7 @@
         <v>45983000</v>
       </c>
       <c r="E54" s="3">
-        <v>45188000</v>
+        <v>45319000</v>
       </c>
       <c r="F54" s="3">
         <v>44836000</v>
@@ -3413,7 +3413,7 @@
         <v>7448000</v>
       </c>
       <c r="E57" s="3">
-        <v>5872000</v>
+        <v>8802000</v>
       </c>
       <c r="F57" s="3">
         <v>6172000</v>
@@ -3475,7 +3475,7 @@
         <v>2451000</v>
       </c>
       <c r="E58" s="3">
-        <v>1751000</v>
+        <v>1729000</v>
       </c>
       <c r="F58" s="3">
         <v>1610000</v>
@@ -3537,7 +3537,7 @@
         <v>1328000</v>
       </c>
       <c r="E59" s="3">
-        <v>1266000</v>
+        <v>4648000</v>
       </c>
       <c r="F59" s="3">
         <v>1497000</v>
@@ -3599,7 +3599,7 @@
         <v>11227000</v>
       </c>
       <c r="E60" s="3">
-        <v>8889000</v>
+        <v>8041000</v>
       </c>
       <c r="F60" s="3">
         <v>9279000</v>
@@ -3658,25 +3658,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8644000</v>
+        <v>7563000</v>
       </c>
       <c r="E61" s="3">
-        <v>9204000</v>
+        <v>9145000</v>
       </c>
       <c r="F61" s="3">
-        <v>9598000</v>
+        <v>8584000</v>
       </c>
       <c r="G61" s="3">
-        <v>11312000</v>
+        <v>9938000</v>
       </c>
       <c r="H61" s="3">
-        <v>11995000</v>
+        <v>10659000</v>
       </c>
       <c r="I61" s="3">
-        <v>12297000</v>
+        <v>10958000</v>
       </c>
       <c r="J61" s="3">
-        <v>16434000</v>
+        <v>15108000</v>
       </c>
       <c r="K61" s="3">
         <v>10604000</v>
@@ -3720,25 +3720,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4766000</v>
+        <v>5847000</v>
       </c>
       <c r="E62" s="3">
-        <v>4758000</v>
+        <v>8042000</v>
       </c>
       <c r="F62" s="3">
-        <v>4524000</v>
+        <v>5538000</v>
       </c>
       <c r="G62" s="3">
-        <v>4863000</v>
+        <v>6237000</v>
       </c>
       <c r="H62" s="3">
-        <v>4550000</v>
+        <v>5886000</v>
       </c>
       <c r="I62" s="3">
-        <v>4834000</v>
+        <v>6173000</v>
       </c>
       <c r="J62" s="3">
-        <v>4674000</v>
+        <v>6000000</v>
       </c>
       <c r="K62" s="3">
         <v>4507000</v>
@@ -3971,7 +3971,7 @@
         <v>25288000</v>
       </c>
       <c r="E66" s="3">
-        <v>23497000</v>
+        <v>23162000</v>
       </c>
       <c r="F66" s="3">
         <v>24041000</v>
@@ -4305,7 +4305,7 @@
         <v>22041000</v>
       </c>
       <c r="E72" s="3">
-        <v>22372000</v>
+        <v>22875000</v>
       </c>
       <c r="F72" s="3">
         <v>21746000</v>
@@ -4553,7 +4553,7 @@
         <v>20694000</v>
       </c>
       <c r="E76" s="3">
-        <v>21690000</v>
+        <v>22156000</v>
       </c>
       <c r="F76" s="3">
         <v>20794000</v>
@@ -4744,7 +4744,7 @@
         <v>1168000</v>
       </c>
       <c r="E81" s="3">
-        <v>1753000</v>
+        <v>3862000</v>
       </c>
       <c r="F81" s="3">
         <v>2094000</v>
@@ -4830,7 +4830,7 @@
         <v>893000</v>
       </c>
       <c r="E83" s="3">
-        <v>896000</v>
+        <v>1757000</v>
       </c>
       <c r="F83" s="3">
         <v>861000</v>
@@ -5202,7 +5202,7 @@
         <v>998000</v>
       </c>
       <c r="E89" s="3">
-        <v>3333000</v>
+        <v>3954000</v>
       </c>
       <c r="F89" s="3">
         <v>621000</v>
@@ -5474,7 +5474,7 @@
         <v>-906000</v>
       </c>
       <c r="E94" s="3">
-        <v>-3009000</v>
+        <v>-884000</v>
       </c>
       <c r="F94" s="3">
         <v>2125000</v>
@@ -5560,7 +5560,7 @@
         <v>-761000</v>
       </c>
       <c r="E96" s="3">
-        <v>-185000</v>
+        <v>-917000</v>
       </c>
       <c r="F96" s="3">
         <v>-732000</v>
@@ -5808,7 +5808,7 @@
         <v>-1845000</v>
       </c>
       <c r="E100" s="3">
-        <v>-1216000</v>
+        <v>-2686000</v>
       </c>
       <c r="F100" s="3">
         <v>-1470000</v>
@@ -5870,7 +5870,7 @@
         <v>92000</v>
       </c>
       <c r="E101" s="3">
-        <v>2000</v>
+        <v>-231000</v>
       </c>
       <c r="F101" s="3">
         <v>-233000</v>
@@ -5932,7 +5932,7 @@
         <v>-1661000</v>
       </c>
       <c r="E102" s="3">
-        <v>-890000</v>
+        <v>153000</v>
       </c>
       <c r="F102" s="3">
         <v>1043000</v>

--- a/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>CRH</t>
   </si>
@@ -656,22 +656,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -680,268 +680,294 @@
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43738</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43281</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>42916</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42735</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42551</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42369</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42185</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6533000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>34949000</v>
+      </c>
+      <c r="F8" s="3">
         <v>16136000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>32723000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>14998000</v>
       </c>
-      <c r="G8" s="3">
-        <v>16039000</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
+        <v>29206000</v>
+      </c>
+      <c r="J8" s="3">
         <v>13167000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>15372000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>12215000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>15285000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>8583000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>12847000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>27449000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>11944000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>11726300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>13125100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>27218300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>14241400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>16005200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>10998600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>12428300</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4726000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>22986000</v>
+      </c>
+      <c r="F9" s="3">
         <v>10855000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>21908000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>10243000</v>
       </c>
-      <c r="G9" s="3">
-        <v>10483000</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>19379000</v>
+      </c>
+      <c r="J9" s="3">
         <v>8867000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>10060000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>8365000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>10130000</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="3">
         <v>8729000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>18391000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>8236000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>7398500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>8960500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>18189500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>9780400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>10894500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>7845700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>8641600</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1807000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>11963000</v>
+      </c>
+      <c r="F10" s="3">
         <v>5281000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>10815000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>4755000</v>
       </c>
-      <c r="G10" s="3">
-        <v>5556000</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>9827000</v>
+      </c>
+      <c r="J10" s="3">
         <v>4300000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5312000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>3850000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>5155000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>4118000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>9058000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>3708000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>4327900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4164600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>9028900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>4461000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>5110700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>3152900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>3786700</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -964,8 +990,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1026,8 +1054,14 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1088,59 +1122,65 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>367000</v>
+      </c>
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
-        <v>35000</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
+        <v>146000</v>
+      </c>
+      <c r="H14" s="3">
         <v>4000</v>
       </c>
-      <c r="G14" s="3">
-        <v>12000</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>25000</v>
+      </c>
+      <c r="J14" s="3">
         <v>2000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>1000</v>
       </c>
       <c r="K14" s="3">
         <v>5000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>1000</v>
       </c>
       <c r="M14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>21000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>12000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>5500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1150,31 +1190,37 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
+        <v>139000</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
+        <v>103000</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+        <v>46000</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1212,8 +1258,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1233,132 +1285,146 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6345000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>30763000</v>
+      </c>
+      <c r="F17" s="3">
         <v>14509000</v>
       </c>
-      <c r="E17" s="3">
-        <v>28914000</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
+        <v>29013000</v>
+      </c>
+      <c r="H17" s="3">
         <v>13613000</v>
       </c>
-      <c r="G17" s="3">
-        <v>13733000</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>25879000</v>
+      </c>
+      <c r="J17" s="3">
         <v>12142000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>13873000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>11451000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>13288000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="3">
         <v>12051000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>25003000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>11352000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>10147400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>12452700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>25123300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>13581700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>14784500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>10776700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>11552600</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4186000</v>
+      </c>
+      <c r="F18" s="3">
         <v>1627000</v>
       </c>
-      <c r="E18" s="3">
-        <v>3809000</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>3710000</v>
+      </c>
+      <c r="H18" s="3">
         <v>1385000</v>
       </c>
-      <c r="G18" s="3">
-        <v>2306000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>3327000</v>
+      </c>
+      <c r="J18" s="3">
         <v>1025000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1499000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>764000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1997000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="3">
         <v>796000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2446000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>592000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1579000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>672300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>2095000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>659700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1220700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>221900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>875700</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1381,155 +1447,169 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-89000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-169000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-117000</v>
       </c>
-      <c r="E20" s="3">
-        <v>-348000</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>-246000</v>
+      </c>
+      <c r="H20" s="3">
         <v>-182000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-132000</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>-222000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-96000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-353000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-246000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-533000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3">
         <v>-79000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-478000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-95000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-131600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-146200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-316200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-203100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-132400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-147900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>496000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5650000</v>
+      </c>
+      <c r="F21" s="3">
         <v>2403000</v>
       </c>
-      <c r="E21" s="3">
-        <v>5218000</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>5041000</v>
+      </c>
+      <c r="H21" s="3">
         <v>2064000</v>
       </c>
-      <c r="G21" s="3">
-        <v>3091000</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>4870000</v>
+      </c>
+      <c r="J21" s="3">
         <v>1777000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2014000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1344000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>272000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2233000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1015000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2098100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1110900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>2964600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1053500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1685200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>503600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1221900</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+        <v>3000</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+        <v>3000</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>3000</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1567,132 +1647,150 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4014000</v>
+      </c>
+      <c r="F23" s="3">
         <v>1510000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>3461000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1203000</v>
       </c>
-      <c r="G23" s="3">
-        <v>2174000</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>3102000</v>
+      </c>
+      <c r="J23" s="3">
         <v>929000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1146000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>518000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1464000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="3">
         <v>717000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1968000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>497000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1447400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>526100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1778800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>456600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1088300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>74000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>821700</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>925000</v>
+      </c>
+      <c r="F24" s="3">
         <v>332000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>762000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>265000</v>
       </c>
-      <c r="G24" s="3">
-        <v>460000</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>650000</v>
+      </c>
+      <c r="J24" s="3">
         <v>201000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>387000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>112000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>375000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="3">
         <v>159000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>467000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>119000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-140000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>142900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>473200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>127900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>323100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>18800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1753,132 +1851,150 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3089000</v>
+      </c>
+      <c r="F26" s="3">
         <v>1178000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2699000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>938000</v>
       </c>
-      <c r="G26" s="3">
-        <v>1714000</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>2452000</v>
+      </c>
+      <c r="J26" s="3">
         <v>728000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>759000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>406000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1089000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="3">
         <v>558000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1501000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>378000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1587400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>383200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1305500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>328700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>765200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>55200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>631500</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3178000</v>
+      </c>
+      <c r="F27" s="3">
         <v>1168000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2672000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>926000</v>
       </c>
-      <c r="G27" s="3">
-        <v>1688000</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>2451000</v>
+      </c>
+      <c r="J27" s="3">
         <v>698000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>719000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>403000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1076000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="3">
         <v>551000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1497000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>378000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1570600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>373300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1275900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>313000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>760700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>54000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1939,70 +2055,82 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="3">
-        <v>1190000</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1212000</v>
+      </c>
+      <c r="H29" s="3">
         <v>1168000</v>
       </c>
-      <c r="G29" s="3">
-        <v>92000</v>
-      </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
+        <v>271000</v>
+      </c>
+      <c r="J29" s="3">
         <v>87000</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>47000</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3">
         <v>42000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>1388000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>1083000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>915100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>28800</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>88900</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2063,8 +2191,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2125,132 +2259,150 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>169000</v>
+      </c>
+      <c r="F32" s="3">
         <v>117000</v>
       </c>
-      <c r="E32" s="3">
-        <v>348000</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>246000</v>
+      </c>
+      <c r="H32" s="3">
         <v>182000</v>
       </c>
-      <c r="G32" s="3">
-        <v>132000</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>222000</v>
+      </c>
+      <c r="J32" s="3">
         <v>96000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>353000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>246000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>533000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3">
         <v>79000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>478000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>95000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>131600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>146200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>316200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>203100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>132400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>147900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>54000</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3178000</v>
+      </c>
+      <c r="F33" s="3">
         <v>1168000</v>
       </c>
-      <c r="E33" s="3">
-        <v>3862000</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>3884000</v>
+      </c>
+      <c r="H33" s="3">
         <v>2094000</v>
       </c>
-      <c r="G33" s="3">
-        <v>1780000</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>2722000</v>
+      </c>
+      <c r="J33" s="3">
         <v>785000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>719000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>403000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1123000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" s="3">
         <v>593000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2885000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1461000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2485700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>402100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1364800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>313000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>760700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>54000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2311,137 +2463,155 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3178000</v>
+      </c>
+      <c r="F35" s="3">
         <v>1168000</v>
       </c>
-      <c r="E35" s="3">
-        <v>3862000</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>3884000</v>
+      </c>
+      <c r="H35" s="3">
         <v>2094000</v>
       </c>
-      <c r="G35" s="3">
-        <v>1780000</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>2722000</v>
+      </c>
+      <c r="J35" s="3">
         <v>785000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>719000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>403000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1123000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O35" s="3">
         <v>593000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2885000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1461000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2485700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>402100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1364800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>313000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>760700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>54000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43738</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43281</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>42916</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42735</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42551</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42369</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42185</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2464,8 +2634,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2488,70 +2660,78 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3308000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6341000</v>
+      </c>
+      <c r="F41" s="3">
         <v>4275000</v>
       </c>
-      <c r="E41" s="3">
-        <v>5936000</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>11872000</v>
+      </c>
+      <c r="H41" s="3">
         <v>6826000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5783000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6292000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7721000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>14661000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9918000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1592000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9191000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1848000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1848000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2530000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2137700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2689000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1564100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2825200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>6149600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3829000</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2612,442 +2792,490 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4798000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4507000</v>
+      </c>
+      <c r="F43" s="3">
         <v>6450000</v>
       </c>
-      <c r="E43" s="3">
-        <v>4363000</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
+        <v>8932000</v>
+      </c>
+      <c r="H43" s="3">
         <v>5858000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4611000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5335000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>4122000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4946000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4253000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>6008000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4682000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>5091000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>5091000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4539600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>5396200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4373300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>5548200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>4467800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>4211600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>3121200</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4619000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>4291000</v>
+      </c>
+      <c r="F44" s="3">
         <v>4276000</v>
       </c>
-      <c r="E44" s="3">
-        <v>4194000</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
+        <v>8388000</v>
+      </c>
+      <c r="H44" s="3">
         <v>3792000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>3611000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>3193000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3117000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2940000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3080000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>3673000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3505000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>3151000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>3151000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>3247700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>3450200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>3227000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3362600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3223500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>2978000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>2652800</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>984000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1746000</v>
+      </c>
+      <c r="F45" s="3">
         <v>8000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>442000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>112000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>39000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>35000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>17000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>27000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>7000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>10000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>17000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>31000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>31000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1370800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>66500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>25300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>29200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>26900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>25800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>640900</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13709000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>16885000</v>
+      </c>
+      <c r="F46" s="3">
         <v>15009000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>14833000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>16588000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>14044000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>14855000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>14977000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>22574000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>17258000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>11283000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17395000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>10121000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10121000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>11688100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>11050500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>10314600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>10504100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>10543300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>13365000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>10243800</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>609000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>620000</v>
+      </c>
+      <c r="F47" s="3">
         <v>885000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>827000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>879000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>904000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>875000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>964000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1049000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1144000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1575000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1565000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1299000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1299000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1709400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1641500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1687600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1688600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1676300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1814700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1686800</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20163000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>19133000</v>
+      </c>
+      <c r="F48" s="3">
         <v>19322000</v>
       </c>
-      <c r="E48" s="3">
-        <v>36606000</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>37864000</v>
+      </c>
+      <c r="H48" s="3">
         <v>18298000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>19502000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>19100000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>19317000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>19099000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>39148000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>38153000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>18046000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>15607000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>15607000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>15663000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>13744200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>13933600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>14146000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>14655400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>9181500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>8712000</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11218000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10199000</v>
+      </c>
+      <c r="F49" s="3">
         <v>10399000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>20574000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>8726000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>9848000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>9468000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>9373000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>9378000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>9475000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>9702000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>9656000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>8615000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>8615000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>8629400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>8360200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>8521600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>8629200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>8774000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>5177700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>4898300</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3108,8 +3336,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3170,70 +3404,82 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>634000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>632000</v>
+      </c>
+      <c r="F52" s="3">
         <v>368000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>959000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>345000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>372000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>231000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>313000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>275000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>161000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>166000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>115000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>114000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>114000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>149500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>200500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>232800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>362400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>262500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>253500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>302800</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3294,70 +3540,82 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>46333000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>47469000</v>
+      </c>
+      <c r="F54" s="3">
         <v>45983000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>45319000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>44836000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>44670000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>44529000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>44944000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>52375000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>47612000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>43034000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>46777000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>35756000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>35756000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>37839400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>34996800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>34690200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>35330300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>35911500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>29792500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>25843800</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3380,8 +3638,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3404,380 +3664,418 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2730000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3149000</v>
+      </c>
+      <c r="F57" s="3">
         <v>7448000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>8802000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6172000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>5692000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6198000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4792000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5031000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4916000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>5773000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5277000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5155000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5155000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5423600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5538000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>5286900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5880300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>5341800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>4145900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3397000</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2992000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1897000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2451000</v>
       </c>
-      <c r="E58" s="3">
-        <v>1729000</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>3004000</v>
+      </c>
+      <c r="H58" s="3">
         <v>1610000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>846000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>452000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1553000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6185000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6920000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1571000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>7213000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1356000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1356000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>378000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>463000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>302000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>720300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>848200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>412000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>524700</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4275000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4967000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1328000</v>
       </c>
-      <c r="E59" s="3">
-        <v>4648000</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
+        <v>4864000</v>
+      </c>
+      <c r="H59" s="3">
         <v>1497000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1043000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1262000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1120000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1125000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1030000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1005000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>976000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>984000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>984000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1412700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>898300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>887200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>880800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>955900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>322800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>617400</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9997000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>10013000</v>
+      </c>
+      <c r="F60" s="3">
         <v>11227000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>8041000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>9279000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7581000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7912000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7465000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>12341000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>12866000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8349000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13466000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7495000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>7495000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>7214300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>6899200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>6476000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>7481400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>7146000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>4880700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4539100</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7563000</v>
+        <v>9680000</v>
       </c>
       <c r="E61" s="3">
-        <v>9145000</v>
+        <v>9862000</v>
       </c>
       <c r="F61" s="3">
-        <v>8584000</v>
+        <v>8644000</v>
       </c>
       <c r="G61" s="3">
-        <v>9938000</v>
+        <v>8204000</v>
       </c>
       <c r="H61" s="3">
-        <v>10659000</v>
+        <v>9598000</v>
       </c>
       <c r="I61" s="3">
+        <v>11312000</v>
+      </c>
+      <c r="J61" s="3">
+        <v>11995000</v>
+      </c>
+      <c r="K61" s="3">
         <v>10958000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>15108000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>10604000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>11731000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>9959000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>8557000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>8557000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>9162900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8838600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>8251500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>8908600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>9497600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>7241200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>6360900</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5847000</v>
+        <v>5914000</v>
       </c>
       <c r="E62" s="3">
-        <v>8042000</v>
+        <v>5973000</v>
       </c>
       <c r="F62" s="3">
-        <v>5538000</v>
+        <v>4766000</v>
       </c>
       <c r="G62" s="3">
-        <v>6237000</v>
+        <v>7924000</v>
       </c>
       <c r="H62" s="3">
-        <v>5886000</v>
+        <v>4524000</v>
       </c>
       <c r="I62" s="3">
+        <v>4863000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>4550000</v>
+      </c>
+      <c r="K62" s="3">
         <v>6173000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>6000000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4507000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>4543000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4400000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3733000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3733000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3546700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3845600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4104300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>4229900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>4071700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2946300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2973300</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3838,8 +4136,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3900,8 +4204,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3962,70 +4272,82 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26318000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>26615000</v>
+      </c>
+      <c r="F66" s="3">
         <v>25288000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>23162000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>24041000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>24437000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>25152000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>25288000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>34091000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>28584000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>25243000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>28427000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>20279000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>20279000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>20505300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>20143900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>19433500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>21220200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>21308800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>15094000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>13897900</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4048,8 +4370,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4110,8 +4434,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4172,8 +4502,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4187,7 +4523,7 @@
         <v>1000</v>
       </c>
       <c r="G70" s="3">
-        <v>1000</v>
+        <v>302000</v>
       </c>
       <c r="H70" s="3">
         <v>1000</v>
@@ -4214,13 +4550,13 @@
         <v>1000</v>
       </c>
       <c r="P70" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R70" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>1100</v>
-      </c>
-      <c r="R70" s="3">
-        <v>1100</v>
       </c>
       <c r="S70" s="3">
         <v>1100</v>
@@ -4229,13 +4565,19 @@
         <v>1100</v>
       </c>
       <c r="U70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W70" s="3">
         <v>1200</v>
       </c>
-      <c r="V70" s="3">
+      <c r="X70" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4296,70 +4638,82 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22346000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>22918000</v>
+      </c>
+      <c r="F72" s="3">
         <v>22041000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>22875000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>21746000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>20215000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>19463000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>12009000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>11501000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>11761000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>11929000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>12083000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>9126000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>9126000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>9794500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>7499600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>7420300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>6436900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>6776800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>6156600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>6344400</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4420,8 +4774,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4482,8 +4842,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4544,70 +4910,82 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20014000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>20853000</v>
+      </c>
+      <c r="F76" s="3">
         <v>20694000</v>
       </c>
-      <c r="E76" s="3">
-        <v>22156000</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>21855000</v>
+      </c>
+      <c r="H76" s="3">
         <v>20794000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>20232000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>19376000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>19655000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>18283000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>19027000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>17790000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>18349000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>15476000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>15476000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>17332900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>14851800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>15255600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>14109000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>14601600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>14697300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>11944700</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4668,137 +5046,155 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43738</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43281</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>42916</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42735</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42551</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42369</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42185</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3178000</v>
+      </c>
+      <c r="F81" s="3">
         <v>1168000</v>
       </c>
-      <c r="E81" s="3">
-        <v>3862000</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>3884000</v>
+      </c>
+      <c r="H81" s="3">
         <v>2094000</v>
       </c>
-      <c r="G81" s="3">
-        <v>1780000</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>2722000</v>
+      </c>
+      <c r="J81" s="3">
         <v>785000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>719000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>403000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1123000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O81" s="3">
         <v>593000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2885000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1461000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2485700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>402100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1364800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>313000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>760700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>54000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4821,70 +5217,78 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1633000</v>
+      </c>
+      <c r="F83" s="3">
         <v>893000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1757000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>861000</v>
       </c>
-      <c r="G83" s="3">
-        <v>917000</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
+        <v>1765000</v>
+      </c>
+      <c r="J83" s="3">
         <v>848000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>868000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>826000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>-445000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>265000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>518000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>650700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>584800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1185800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>596900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>596900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>429600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4945,8 +5349,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5007,8 +5417,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5069,8 +5485,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5131,8 +5553,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5193,70 +5621,82 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-712000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>5017000</v>
+      </c>
+      <c r="F89" s="3">
         <v>998000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>3954000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>621000</v>
       </c>
-      <c r="G89" s="3">
-        <v>2645000</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>4210000</v>
+      </c>
+      <c r="J89" s="3">
         <v>1565000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2930000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1008000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O89" s="3">
         <v>-1940000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>57000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-311000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2677100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-54300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>2569300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>77400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2822900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-315800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1747800</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5279,70 +5719,78 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-506000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1046000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-771000</v>
       </c>
-      <c r="E91" s="3">
-        <v>-927000</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
+        <v>-958000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-596000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-967000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-587000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-482000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-514000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-656000</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O91" s="3">
         <v>486000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-77000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-509000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-635200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-568200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-936600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-457800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-610400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-396700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-260600</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5403,8 +5851,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5465,70 +5919,82 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2096000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2391000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-906000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-884000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>2125000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-2027000</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>-2546000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-519000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-613000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-447000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>1026000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>1093000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1321000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2039500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1085400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-807000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-445400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-8485600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>301700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5551,70 +6017,78 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-750000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-940000</v>
+      </c>
+      <c r="F96" s="3">
         <v>-761000</v>
       </c>
-      <c r="E96" s="3">
-        <v>-917000</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
+        <v>-906000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-732000</v>
       </c>
-      <c r="G96" s="3">
-        <v>-177000</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
+        <v>-906000</v>
+      </c>
+      <c r="J96" s="3">
         <v>-729000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-170000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-537000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>96000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-52000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-358000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-116000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-412000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-386500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-260300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-161600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-275800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-135000</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5675,8 +6149,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5737,8 +6217,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5799,190 +6285,214 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-176000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2380000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1845000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-2686000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1470000</v>
       </c>
-      <c r="G100" s="3">
-        <v>-937000</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>-3305000</v>
+      </c>
+      <c r="J100" s="3">
         <v>-2368000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-4992000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>5279000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>-544000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-456000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1337000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-311000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>667900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1901700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-859400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>2637800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>2125800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>610400</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>208000</v>
+      </c>
+      <c r="F101" s="3">
         <v>92000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-231000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-233000</v>
       </c>
-      <c r="G101" s="3">
-        <v>-190000</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
+        <v>-297000</v>
+      </c>
+      <c r="J101" s="3">
         <v>-107000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>308000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>30000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
         <v>-11000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>178000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>8000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-81300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-103000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>63700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-33700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-28000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>170200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>132600</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3081000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>454000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1661000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>153000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1043000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-509000</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>-1938000</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1429000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2367000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>5870000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O102" s="3">
         <v>-1158000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>525000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-287000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>245200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-574800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-75800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1261100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-3052900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>2281900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2522500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>CRH</t>
   </si>
@@ -1455,7 +1455,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-89000</v>
+        <v>44000</v>
       </c>
       <c r="E20" s="3">
         <v>-169000</v>
@@ -1523,7 +1523,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>496000</v>
+        <v>629000</v>
       </c>
       <c r="E21" s="3">
         <v>5650000</v>
@@ -1590,8 +1590,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>133000</v>
       </c>
       <c r="E22" s="3">
         <v>3000</v>
@@ -2271,7 +2271,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>89000</v>
+        <v>-44000</v>
       </c>
       <c r="E32" s="3">
         <v>169000</v>

--- a/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
   <si>
     <t>CRH</t>
   </si>
@@ -656,24 +656,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -682,292 +681,318 @@
     <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
-        <v>45291</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43738</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42916</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42735</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42551</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42369</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42185</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10515000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9654000</v>
+      </c>
+      <c r="F8" s="3">
         <v>6533000</v>
       </c>
-      <c r="E8" s="3">
-        <v>34949000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>16136000</v>
-      </c>
       <c r="G8" s="3">
-        <v>32723000</v>
+        <v>10128000</v>
       </c>
       <c r="H8" s="3">
-        <v>14998000</v>
+        <v>9709000</v>
       </c>
       <c r="I8" s="3">
+        <v>6427000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>8862500</v>
+      </c>
+      <c r="K8" s="3">
         <v>29206000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>13167000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>15372000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>12215000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>15285000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>8583000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>12847000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>27449000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>11944000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>11726300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>13125100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>27218300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>14241400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>16005200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>10998600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>12428300</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6456000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5979000</v>
+      </c>
+      <c r="F9" s="3">
         <v>4726000</v>
       </c>
-      <c r="E9" s="3">
-        <v>22986000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>10855000</v>
-      </c>
       <c r="G9" s="3">
-        <v>21908000</v>
+        <v>6365000</v>
       </c>
       <c r="H9" s="3">
-        <v>10243000</v>
+        <v>6079000</v>
       </c>
       <c r="I9" s="3">
+        <v>4808000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>5832500</v>
+      </c>
+      <c r="K9" s="3">
         <v>19379000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>8867000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>10060000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>8365000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>10130000</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
         <v>8729000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>18391000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>8236000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>7398500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>8960500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>18189500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>9780400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>10894500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>7845700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>8641600</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4059000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3675000</v>
+      </c>
+      <c r="F10" s="3">
         <v>1807000</v>
       </c>
-      <c r="E10" s="3">
-        <v>11963000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>5281000</v>
-      </c>
       <c r="G10" s="3">
-        <v>10815000</v>
+        <v>3763000</v>
       </c>
       <c r="H10" s="3">
-        <v>4755000</v>
+        <v>3630000</v>
       </c>
       <c r="I10" s="3">
+        <v>1619000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3030000</v>
+      </c>
+      <c r="K10" s="3">
         <v>9827000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4300000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>5312000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3850000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>5155000</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3">
         <v>4118000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>9058000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>3708000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4327900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>4164600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>9028900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>4461000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>5110700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>3152900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>3786700</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -992,8 +1017,10 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1060,8 +1087,14 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1128,65 +1161,71 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-160000</v>
+        <v>-120000</v>
       </c>
       <c r="E14" s="3">
-        <v>367000</v>
+        <v>-121000</v>
       </c>
       <c r="F14" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>45500</v>
+      </c>
+      <c r="K14" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L14" s="3">
         <v>2000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>146000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>25000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1000</v>
       </c>
       <c r="M14" s="3">
         <v>5000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>1000</v>
       </c>
       <c r="O14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>21000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>12000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>5500</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1196,37 +1235,43 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>467000</v>
       </c>
       <c r="E15" s="3">
-        <v>139000</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
+        <v>424000</v>
+      </c>
+      <c r="F15" s="3">
+        <v>397000</v>
       </c>
       <c r="G15" s="3">
-        <v>103000</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>8</v>
+        <v>402000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>401000</v>
       </c>
       <c r="I15" s="3">
+        <v>384000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>376000</v>
+      </c>
+      <c r="K15" s="3">
         <v>46000</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1264,8 +1309,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1287,144 +1338,158 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6345000</v>
+        <v>8611000</v>
       </c>
       <c r="E17" s="3">
-        <v>30763000</v>
+        <v>7922000</v>
       </c>
       <c r="F17" s="3">
-        <v>14509000</v>
+        <v>6492000</v>
       </c>
       <c r="G17" s="3">
-        <v>29013000</v>
+        <v>8350000</v>
       </c>
       <c r="H17" s="3">
-        <v>13613000</v>
+        <v>8112000</v>
       </c>
       <c r="I17" s="3">
+        <v>6428000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>7641000</v>
+      </c>
+      <c r="K17" s="3">
         <v>25879000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>12142000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>13873000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>11451000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>13288000</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="3">
         <v>12051000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>25003000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>11352000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>10147400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>12452700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>25123300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>13581700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>14784500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>10776700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>11552600</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>188000</v>
+        <v>1904000</v>
       </c>
       <c r="E18" s="3">
-        <v>4186000</v>
+        <v>1732000</v>
       </c>
       <c r="F18" s="3">
-        <v>1627000</v>
+        <v>41000</v>
       </c>
       <c r="G18" s="3">
-        <v>3710000</v>
+        <v>1778000</v>
       </c>
       <c r="H18" s="3">
-        <v>1385000</v>
+        <v>1597000</v>
       </c>
       <c r="I18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1221500</v>
+      </c>
+      <c r="K18" s="3">
         <v>3327000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1025000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1499000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>764000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1997000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="3">
         <v>796000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2446000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>592000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1579000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>672300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>2095000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>659700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1220700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>221900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>875700</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1449,173 +1514,187 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>44000</v>
+        <v>-27000</v>
       </c>
       <c r="E20" s="3">
-        <v>-169000</v>
+        <v>-5000</v>
       </c>
       <c r="F20" s="3">
-        <v>-117000</v>
+        <v>4000</v>
       </c>
       <c r="G20" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-222000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-353000</v>
+      </c>
+      <c r="N20" s="3">
         <v>-246000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-182000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-222000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-96000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-353000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-246000</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-533000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-79000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-478000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-95000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-131600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-146200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-316200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-203100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-132400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-147900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>629000</v>
+        <v>2398000</v>
       </c>
       <c r="E21" s="3">
-        <v>5650000</v>
+        <v>2161000</v>
       </c>
       <c r="F21" s="3">
-        <v>2403000</v>
+        <v>434000</v>
       </c>
       <c r="G21" s="3">
-        <v>5041000</v>
+        <v>2194000</v>
       </c>
       <c r="H21" s="3">
-        <v>2064000</v>
+        <v>2011000</v>
       </c>
       <c r="I21" s="3">
+        <v>377000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1603500</v>
+      </c>
+      <c r="K21" s="3">
         <v>4870000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1777000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2014000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1344000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>272000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2233000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1015000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>2098100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1110900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>2964600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1053500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1685200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>503600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1221900</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>155000</v>
+      </c>
+      <c r="F22" s="3">
         <v>133000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
+        <v>131000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>73000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>81000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>82000</v>
+      </c>
+      <c r="K22" s="3">
         <v>3000</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1653,144 +1732,162 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>99000</v>
+        <v>1920000</v>
       </c>
       <c r="E23" s="3">
-        <v>4014000</v>
+        <v>1739000</v>
       </c>
       <c r="F23" s="3">
-        <v>1510000</v>
+        <v>95000</v>
       </c>
       <c r="G23" s="3">
-        <v>3461000</v>
+        <v>1734000</v>
       </c>
       <c r="H23" s="3">
-        <v>1203000</v>
+        <v>1591000</v>
       </c>
       <c r="I23" s="3">
+        <v>-45000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="K23" s="3">
         <v>3102000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>929000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1146000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>518000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1464000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="3">
         <v>717000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1968000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>497000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1447400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>526100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1778800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>456600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1088300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>74000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>821700</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>430000</v>
+      </c>
+      <c r="F24" s="3">
         <v>-19000</v>
       </c>
-      <c r="E24" s="3">
-        <v>925000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>332000</v>
-      </c>
       <c r="G24" s="3">
-        <v>762000</v>
+        <v>416000</v>
       </c>
       <c r="H24" s="3">
-        <v>265000</v>
+        <v>379000</v>
       </c>
       <c r="I24" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>248500</v>
+      </c>
+      <c r="K24" s="3">
         <v>650000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>201000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>387000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>112000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>375000</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
         <v>159000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>467000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>119000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-140000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>142900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>473200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>127900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>323100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>18800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1857,144 +1954,162 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>118000</v>
+        <v>1389000</v>
       </c>
       <c r="E26" s="3">
-        <v>3089000</v>
+        <v>1309000</v>
       </c>
       <c r="F26" s="3">
-        <v>1178000</v>
+        <v>114000</v>
       </c>
       <c r="G26" s="3">
-        <v>2699000</v>
+        <v>1318000</v>
       </c>
       <c r="H26" s="3">
-        <v>938000</v>
+        <v>1212000</v>
       </c>
       <c r="I26" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>880500</v>
+      </c>
+      <c r="K26" s="3">
         <v>2452000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>728000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>759000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>406000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1089000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3">
         <v>558000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1501000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>378000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1587400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>383200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1305500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>328700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>765200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>55200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>631500</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>116000</v>
+        <v>1353000</v>
       </c>
       <c r="E27" s="3">
-        <v>3178000</v>
+        <v>1294000</v>
       </c>
       <c r="F27" s="3">
-        <v>1168000</v>
+        <v>112000</v>
       </c>
       <c r="G27" s="3">
-        <v>2672000</v>
+        <v>1300000</v>
       </c>
       <c r="H27" s="3">
-        <v>926000</v>
+        <v>1197000</v>
       </c>
       <c r="I27" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>904000</v>
+      </c>
+      <c r="K27" s="3">
         <v>2451000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>698000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>719000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>403000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1076000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="3">
         <v>551000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1497000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>378000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1570600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>373300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1275900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>313000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>760700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>54000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2061,13 +2176,19 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2076,61 +2197,67 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>1212000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>1168000</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K29" s="3">
         <v>271000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>87000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>47000</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
         <v>42000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>1388000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>1083000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>915100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>28800</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>88900</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2197,8 +2324,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2265,144 +2398,162 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-44000</v>
+        <v>27000</v>
       </c>
       <c r="E32" s="3">
-        <v>169000</v>
+        <v>5000</v>
       </c>
       <c r="F32" s="3">
-        <v>117000</v>
+        <v>-4000</v>
       </c>
       <c r="G32" s="3">
+        <v>14000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>222000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>96000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>353000</v>
+      </c>
+      <c r="N32" s="3">
         <v>246000</v>
       </c>
-      <c r="H32" s="3">
-        <v>182000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>222000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>96000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>353000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>246000</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>533000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>79000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>478000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>95000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>131600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>146200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>316200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>203100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>132400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>147900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>54000</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1376000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1297000</v>
+      </c>
+      <c r="F33" s="3">
         <v>116000</v>
       </c>
-      <c r="E33" s="3">
-        <v>3178000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1168000</v>
-      </c>
       <c r="G33" s="3">
-        <v>3884000</v>
+        <v>1306000</v>
       </c>
       <c r="H33" s="3">
-        <v>2094000</v>
+        <v>1199000</v>
       </c>
       <c r="I33" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>884000</v>
+      </c>
+      <c r="K33" s="3">
         <v>2722000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>785000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>719000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>403000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1123000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="3">
         <v>593000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2885000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1461000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2485700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>402100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1364800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>313000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>760700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>54000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2469,149 +2620,167 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1376000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1297000</v>
+      </c>
+      <c r="F35" s="3">
         <v>116000</v>
       </c>
-      <c r="E35" s="3">
-        <v>3178000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1168000</v>
-      </c>
       <c r="G35" s="3">
-        <v>3884000</v>
+        <v>1306000</v>
       </c>
       <c r="H35" s="3">
-        <v>2094000</v>
+        <v>1199000</v>
       </c>
       <c r="I35" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>884000</v>
+      </c>
+      <c r="K35" s="3">
         <v>2722000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>785000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>719000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>403000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1123000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="3">
         <v>593000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2885000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1461000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2485700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>402100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1364800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>313000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>760700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>54000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
-        <v>45291</v>
-      </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43738</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42916</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42735</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42551</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42369</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42185</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2636,8 +2805,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2662,76 +2833,84 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2978000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3066000</v>
+      </c>
+      <c r="F41" s="3">
         <v>3308000</v>
       </c>
-      <c r="E41" s="3">
-        <v>6341000</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" s="3">
         <v>4275000</v>
       </c>
-      <c r="G41" s="3">
-        <v>11872000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>6826000</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="3">
+        <v>5936000</v>
+      </c>
+      <c r="K41" s="3">
         <v>5783000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6292000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7721000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>14661000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9918000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1592000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>9191000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1848000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1848000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2530000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2137700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2689000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1564100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2825200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>6149600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3829000</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2798,484 +2977,532 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6422000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5893000</v>
+      </c>
+      <c r="F43" s="3">
         <v>4798000</v>
       </c>
-      <c r="E43" s="3">
-        <v>4507000</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="3">
         <v>6450000</v>
       </c>
-      <c r="G43" s="3">
-        <v>8932000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>5858000</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
+        <v>4300000</v>
+      </c>
+      <c r="K43" s="3">
         <v>4611000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5335000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4122000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4946000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4253000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>6008000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>4682000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>5091000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>5091000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4539600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>5396200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>4373300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>5548200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>4467800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>4211600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>3121200</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4644000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>4514000</v>
+      </c>
+      <c r="F44" s="3">
         <v>4619000</v>
       </c>
-      <c r="E44" s="3">
-        <v>4291000</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3">
         <v>4276000</v>
       </c>
-      <c r="G44" s="3">
-        <v>8388000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>3792000</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
+        <v>4194000</v>
+      </c>
+      <c r="K44" s="3">
         <v>3611000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3193000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3117000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2940000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>3080000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>3673000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>3505000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>3151000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>3151000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>3247700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3450200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3227000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>3362600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>3223500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>2978000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>2652800</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>984000</v>
+        <v>371000</v>
       </c>
       <c r="E45" s="3">
-        <v>1746000</v>
+        <v>428000</v>
       </c>
       <c r="F45" s="3">
+        <v>626000</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>8000</v>
       </c>
-      <c r="G45" s="3">
-        <v>442000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>112000</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
+        <v>134000</v>
+      </c>
+      <c r="K45" s="3">
         <v>39000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>35000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>17000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>27000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>7000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>10000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>17000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>31000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>31000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1370800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>66500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>25300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>29200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>26900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>25800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>640900</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14840000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>15113000</v>
+      </c>
+      <c r="F46" s="3">
         <v>13709000</v>
       </c>
-      <c r="E46" s="3">
-        <v>16885000</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="3">
         <v>15009000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="3">
         <v>14833000</v>
       </c>
-      <c r="H46" s="3">
-        <v>16588000</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>14044000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>14855000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>14977000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>22574000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17258000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>11283000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>17395000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>10121000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>10121000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>11688100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>11050500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>10314600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>10504100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>10543300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>13365000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>10243800</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>929000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>484000</v>
+      </c>
+      <c r="F47" s="3">
         <v>609000</v>
       </c>
-      <c r="E47" s="3">
-        <v>620000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>885000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>827000</v>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3">
-        <v>879000</v>
-      </c>
-      <c r="I47" s="3">
+        <v>714000</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
+        <v>649000</v>
+      </c>
+      <c r="K47" s="3">
         <v>904000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>875000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>964000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1049000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1144000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1575000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1565000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1299000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1299000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1709400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1641500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1687600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1688600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1676300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1814700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1686800</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22611000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>20514000</v>
+      </c>
+      <c r="F48" s="3">
         <v>20163000</v>
       </c>
-      <c r="E48" s="3">
-        <v>19133000</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="3">
         <v>19322000</v>
       </c>
-      <c r="G48" s="3">
-        <v>37864000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>18298000</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
+        <v>18943000</v>
+      </c>
+      <c r="K48" s="3">
         <v>19502000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>19100000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>19317000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>19099000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>39148000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>38153000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>18046000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>15607000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>15607000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>15663000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>13744200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>13933600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>14146000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>14655400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>9181500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>8712000</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12011000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>11337000</v>
+      </c>
+      <c r="F49" s="3">
         <v>11218000</v>
       </c>
-      <c r="E49" s="3">
-        <v>10199000</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>10399000</v>
       </c>
-      <c r="G49" s="3">
-        <v>20574000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>8726000</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>10287000</v>
+      </c>
+      <c r="K49" s="3">
         <v>9848000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>9468000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>9373000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>9378000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>9475000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>9702000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>9656000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>8615000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>8615000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>8629400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>8360200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>8521600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>8629200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>8774000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>5177700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>4898300</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3342,8 +3569,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3410,76 +3643,88 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>830000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>657000</v>
+      </c>
+      <c r="F52" s="3">
         <v>634000</v>
       </c>
-      <c r="E52" s="3">
-        <v>632000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>368000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>959000</v>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H52" s="3">
-        <v>345000</v>
-      </c>
-      <c r="I52" s="3">
+        <v>456000</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
+        <v>607000</v>
+      </c>
+      <c r="K52" s="3">
         <v>372000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>231000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>313000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>275000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>161000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>166000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>115000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>114000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>114000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>149500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>200500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>232800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>362400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>262500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>253500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>302800</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3546,76 +3791,88 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>51221000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>48105000</v>
+      </c>
+      <c r="F54" s="3">
         <v>46333000</v>
       </c>
-      <c r="E54" s="3">
-        <v>47469000</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H54" s="3">
         <v>45983000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" s="3">
         <v>45319000</v>
       </c>
-      <c r="H54" s="3">
-        <v>44836000</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>44670000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>44529000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>44944000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>52375000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>47612000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>43034000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>46777000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>35756000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>35756000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>37839400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>34996800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>34690200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>35330300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>35911500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>29792500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>25843800</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3640,8 +3897,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3666,416 +3925,454 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2963000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3363000</v>
+      </c>
+      <c r="F57" s="3">
         <v>2730000</v>
       </c>
-      <c r="E57" s="3">
-        <v>3149000</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3">
         <v>7448000</v>
       </c>
-      <c r="G57" s="3">
-        <v>8802000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>6172000</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2930000</v>
+      </c>
+      <c r="K57" s="3">
         <v>5692000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6198000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4792000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>5031000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4916000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5773000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5277000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5155000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5155000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>5423600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5538000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>5286900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5880300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>5341800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>4145900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3397000</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2992000</v>
+        <v>3549000</v>
       </c>
       <c r="E58" s="3">
-        <v>1897000</v>
+        <v>3477000</v>
       </c>
       <c r="F58" s="3">
-        <v>2451000</v>
+        <v>3247000</v>
       </c>
       <c r="G58" s="3">
-        <v>3004000</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>1610000</v>
+        <v>2490000</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="K58" s="3">
         <v>846000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>452000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1553000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>6185000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>6920000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1571000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>7213000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1356000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1356000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>378000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>463000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>302000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>720300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>848200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>412000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>524700</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4275000</v>
+        <v>1465000</v>
       </c>
       <c r="E59" s="3">
-        <v>4967000</v>
+        <v>1274000</v>
       </c>
       <c r="F59" s="3">
-        <v>1328000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>4864000</v>
+        <v>1620000</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H59" s="3">
-        <v>1497000</v>
-      </c>
-      <c r="I59" s="3">
+        <v>1289000</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1034000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1043000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1262000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1120000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1125000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1030000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1005000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>976000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>984000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>984000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1412700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>898300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>887200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>880800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>955900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>322800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>617400</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10668000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>10548000</v>
+      </c>
+      <c r="F60" s="3">
         <v>9997000</v>
       </c>
-      <c r="E60" s="3">
-        <v>10013000</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H60" s="3">
         <v>11227000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="3">
         <v>8041000</v>
       </c>
-      <c r="H60" s="3">
-        <v>9279000</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7581000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7912000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7465000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>12341000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>12866000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>8349000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>13466000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>7495000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>7495000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>7214300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>6899200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>6476000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>7481400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>7146000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>4880700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>4539100</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9680000</v>
+        <v>11957000</v>
       </c>
       <c r="E61" s="3">
-        <v>9862000</v>
+        <v>11161000</v>
       </c>
       <c r="F61" s="3">
-        <v>8644000</v>
+        <v>10945000</v>
       </c>
       <c r="G61" s="3">
-        <v>8204000</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>9598000</v>
+        <v>8727000</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>9204000</v>
+      </c>
+      <c r="K61" s="3">
         <v>11312000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>11995000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>10958000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>15108000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>10604000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>11731000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>9959000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>8557000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8557000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>9162900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>8838600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>8251500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>8908600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>9497600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>7241200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>6360900</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5914000</v>
+        <v>2005000</v>
       </c>
       <c r="E62" s="3">
-        <v>5973000</v>
+        <v>1781000</v>
       </c>
       <c r="F62" s="3">
-        <v>4766000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>7924000</v>
+        <v>1715000</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H62" s="3">
-        <v>4524000</v>
-      </c>
-      <c r="I62" s="3">
+        <v>1470000</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1877000</v>
+      </c>
+      <c r="K62" s="3">
         <v>4863000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>4550000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>6173000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>6000000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4507000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>4543000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>4400000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3733000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3733000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3546700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3845600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>4104300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>4229900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>4071700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2946300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2973300</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4142,8 +4439,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4210,8 +4513,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4278,76 +4587,88 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>26318000</v>
+        <v>28055000</v>
       </c>
       <c r="E66" s="3">
-        <v>26615000</v>
+        <v>26654000</v>
       </c>
       <c r="F66" s="3">
+        <v>25591000</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H66" s="3">
+        <v>24637000</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" s="3">
+        <v>22279000</v>
+      </c>
+      <c r="K66" s="3">
+        <v>24437000</v>
+      </c>
+      <c r="L66" s="3">
+        <v>25152000</v>
+      </c>
+      <c r="M66" s="3">
         <v>25288000</v>
       </c>
-      <c r="G66" s="3">
-        <v>23162000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>24041000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>24437000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>25152000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>25288000</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>34091000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>28584000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>25243000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>28427000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>20279000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>20279000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>20505300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>20143900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>19433500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>21220200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>21308800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>15094000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>13897900</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4372,8 +4693,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4440,8 +4763,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4508,8 +4837,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4523,7 +4858,7 @@
         <v>1000</v>
       </c>
       <c r="G70" s="3">
-        <v>302000</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>1000</v>
@@ -4556,13 +4891,13 @@
         <v>1000</v>
       </c>
       <c r="R70" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S70" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T70" s="3">
         <v>1200</v>
-      </c>
-      <c r="S70" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T70" s="3">
-        <v>1100</v>
       </c>
       <c r="U70" s="3">
         <v>1100</v>
@@ -4571,13 +4906,19 @@
         <v>1100</v>
       </c>
       <c r="W70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X70" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y70" s="3">
         <v>1200</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Z70" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4644,76 +4985,88 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>23831000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>23030000</v>
+      </c>
+      <c r="F72" s="3">
         <v>22346000</v>
       </c>
-      <c r="E72" s="3">
-        <v>22918000</v>
-      </c>
-      <c r="F72" s="3">
-        <v>22041000</v>
-      </c>
-      <c r="G72" s="3">
-        <v>22875000</v>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H72" s="3">
-        <v>21746000</v>
-      </c>
-      <c r="I72" s="3">
+        <v>21712000</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3">
+        <v>22495000</v>
+      </c>
+      <c r="K72" s="3">
         <v>20215000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>19463000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>12009000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>11501000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>11761000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>11929000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>12083000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>9126000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>9126000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>9794500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>7499600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>7420300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>6436900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>6776800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>6156600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>6344400</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4780,8 +5133,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4848,8 +5207,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4916,76 +5281,88 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21874000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>20725000</v>
+      </c>
+      <c r="F76" s="3">
         <v>20014000</v>
       </c>
-      <c r="E76" s="3">
-        <v>20853000</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H76" s="3">
         <v>20694000</v>
       </c>
-      <c r="G76" s="3">
-        <v>21855000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>20794000</v>
-      </c>
       <c r="I76" s="3">
+        <v>22156000</v>
+      </c>
+      <c r="J76" s="3">
+        <v>22156000</v>
+      </c>
+      <c r="K76" s="3">
         <v>20232000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>19376000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>19655000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>18283000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>19027000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>17790000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>18349000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>15476000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>15476000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>17332900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>14851800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>15255600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>14109000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>14601600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>14697300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>11944700</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5052,149 +5429,167 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
-        <v>45291</v>
-      </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43738</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42916</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42735</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42551</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42369</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42185</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1376000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1297000</v>
+      </c>
+      <c r="F81" s="3">
         <v>116000</v>
       </c>
-      <c r="E81" s="3">
-        <v>3178000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1168000</v>
-      </c>
       <c r="G81" s="3">
-        <v>3884000</v>
+        <v>1306000</v>
       </c>
       <c r="H81" s="3">
-        <v>2094000</v>
+        <v>1199000</v>
       </c>
       <c r="I81" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>884000</v>
+      </c>
+      <c r="K81" s="3">
         <v>2722000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>785000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>719000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>403000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1123000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81" s="3">
         <v>593000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2885000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1461000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2485700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>402100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1364800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>313000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>760700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>54000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5219,76 +5614,84 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>397000</v>
+        <v>401000</v>
       </c>
       <c r="E83" s="3">
-        <v>1633000</v>
+        <v>384000</v>
       </c>
       <c r="F83" s="3">
-        <v>893000</v>
+        <v>339500</v>
       </c>
       <c r="G83" s="3">
-        <v>1757000</v>
+        <v>339500</v>
       </c>
       <c r="H83" s="3">
-        <v>861000</v>
+        <v>397500</v>
       </c>
       <c r="I83" s="3">
+        <v>397500</v>
+      </c>
+      <c r="J83" s="3">
+        <v>309500</v>
+      </c>
+      <c r="K83" s="3">
         <v>1765000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>848000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>868000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>826000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3">
         <v>-445000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>265000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>518000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>650700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>584800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1185800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>596900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>596900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>429600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5355,8 +5758,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5423,8 +5832,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5491,8 +5906,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5559,8 +5980,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5627,76 +6054,88 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1486000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1485000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-712000</v>
       </c>
-      <c r="E89" s="3">
-        <v>5017000</v>
-      </c>
-      <c r="F89" s="3">
-        <v>998000</v>
-      </c>
       <c r="G89" s="3">
-        <v>3954000</v>
+        <v>1631000</v>
       </c>
       <c r="H89" s="3">
-        <v>621000</v>
+        <v>1634000</v>
       </c>
       <c r="I89" s="3">
+        <v>-671000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1589500</v>
+      </c>
+      <c r="K89" s="3">
         <v>4210000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1565000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2930000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1008000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-1940000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>57000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-311000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>2677100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-54300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2569300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>77400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>2822900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-315800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1747800</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5721,76 +6160,84 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-505000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-624000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-506000</v>
       </c>
-      <c r="E91" s="3">
-        <v>-1046000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-771000</v>
-      </c>
       <c r="G91" s="3">
-        <v>-958000</v>
+        <v>-404000</v>
       </c>
       <c r="H91" s="3">
-        <v>-596000</v>
+        <v>-439000</v>
       </c>
       <c r="I91" s="3">
+        <v>-332000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-463500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-967000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-587000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-482000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-514000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-656000</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91" s="3">
         <v>486000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-509000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-635200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-568200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-936600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-457800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-610400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-396700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-260600</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5857,8 +6304,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5925,76 +6378,88 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1788000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-521000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2096000</v>
       </c>
-      <c r="E94" s="3">
-        <v>-2391000</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-906000</v>
-      </c>
       <c r="G94" s="3">
-        <v>-884000</v>
+        <v>-759000</v>
       </c>
       <c r="H94" s="3">
-        <v>2125000</v>
+        <v>-478000</v>
       </c>
       <c r="I94" s="3">
+        <v>-492000</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1521000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2546000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-519000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-613000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-447000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
         <v>1026000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>1093000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1321000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-2039500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1085400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-807000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-445400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-8485600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>301700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6019,76 +6484,84 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-750000</v>
+        <v>238000</v>
       </c>
       <c r="E96" s="3">
-        <v>-940000</v>
+        <v>481000</v>
       </c>
       <c r="F96" s="3">
-        <v>-761000</v>
+        <v>750000</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
+        <v>761000</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
+        <v>92500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-906000</v>
       </c>
-      <c r="H96" s="3">
-        <v>-732000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-906000</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-729000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-170000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-537000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>96000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-52000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-358000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-116000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-412000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-386500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-260300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-161600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-275800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-135000</v>
       </c>
     </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6155,8 +6628,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6223,8 +6702,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6291,208 +6776,232 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-629000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-339000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-176000</v>
       </c>
-      <c r="E100" s="3">
-        <v>-2380000</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-1845000</v>
-      </c>
       <c r="G100" s="3">
-        <v>-2686000</v>
+        <v>649000</v>
       </c>
       <c r="H100" s="3">
-        <v>-1470000</v>
+        <v>-1555000</v>
       </c>
       <c r="I100" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-514500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-3305000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2368000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-4992000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>5279000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-544000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-456000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>1337000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-311000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>667900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1901700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-859400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>2637800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>2125800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>610400</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-97000</v>
+        <v>24000</v>
       </c>
       <c r="E101" s="3">
-        <v>208000</v>
+        <v>68000</v>
       </c>
       <c r="F101" s="3">
-        <v>92000</v>
+        <v>1000</v>
       </c>
       <c r="G101" s="3">
-        <v>-231000</v>
+        <v>1000</v>
       </c>
       <c r="H101" s="3">
-        <v>-233000</v>
+        <v>-116500</v>
       </c>
       <c r="I101" s="3">
+        <v>-116500</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-297000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-107000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>308000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>30000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-11000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>178000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>8000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-81300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-103000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>63700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-33700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-28000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>170200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>132600</v>
       </c>
     </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-866000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>637000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3081000</v>
       </c>
-      <c r="E102" s="3">
-        <v>454000</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-1661000</v>
-      </c>
       <c r="G102" s="3">
-        <v>153000</v>
+        <v>1447000</v>
       </c>
       <c r="H102" s="3">
-        <v>1043000</v>
+        <v>-375000</v>
       </c>
       <c r="I102" s="3">
+        <v>-1286000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-445000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1938000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1429000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2367000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>5870000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-1158000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>525000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-287000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>245200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-574800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-75800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1261100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-3052900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>2281900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>2522500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>CRH</t>
   </si>
@@ -656,343 +656,354 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43738</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43281</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42916</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42735</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42551</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42369</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42185</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8870000</v>
+      </c>
+      <c r="E8" s="3">
         <v>10515000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9654000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6533000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3">
         <v>10128000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>9709000</v>
       </c>
-      <c r="I8" s="3">
-        <v>6427000</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8862500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>29206000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13167000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15372000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12215000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15285000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8583000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12847000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>27449000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11944000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11726300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13125100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>27218300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14241400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16005200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10998600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>12428300</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5710000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6456000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5979000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4726000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3">
         <v>6365000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>6079000</v>
       </c>
-      <c r="I9" s="3">
-        <v>4808000</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5832500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19379000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8867000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10060000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8365000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10130000</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>8729000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18391000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8236000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7398500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8960500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18189500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9780400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10894500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7845700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8641600</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3160000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4059000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3675000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1807000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
         <v>3763000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>3630000</v>
       </c>
-      <c r="I10" s="3">
-        <v>1619000</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3030000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9827000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4300000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5312000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3850000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5155000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>4118000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9058000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3708000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4327900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4164600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9028900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4461000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5110700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3152900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3786700</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1019,8 +1030,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1093,8 +1105,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1167,68 +1182,71 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-120000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-121000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-148000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>-11000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-18000</v>
       </c>
-      <c r="I14" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>45500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>25000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>21000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>5500</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1241,40 +1259,43 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>510000</v>
+      </c>
+      <c r="E15" s="3">
         <v>467000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>424000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>397000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>446000</v>
+      </c>
+      <c r="I15" s="3">
         <v>402000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>401000</v>
       </c>
-      <c r="I15" s="3">
-        <v>384000</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>376000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>46000</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1315,8 +1336,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1340,156 +1364,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7639000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8611000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7922000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6492000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3">
         <v>8350000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8112000</v>
       </c>
-      <c r="I17" s="3">
-        <v>6428000</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7641000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25879000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12142000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13873000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11451000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13288000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>12051000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25003000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11352000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10147400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12452700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25123300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13581700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14784500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10776700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>11552600</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1231000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1904000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1732000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>41000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3">
         <v>1778000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1597000</v>
       </c>
-      <c r="I18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1221500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3327000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1025000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1499000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>764000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1997000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>796000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2446000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>592000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1579000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>672300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2095000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>659700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1220700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>221900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>875700</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1516,188 +1547,195 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-27000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>-14000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-13000</v>
       </c>
-      <c r="I20" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-222000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-96000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-353000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-246000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-533000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>-79000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-478000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-95000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-131600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-146200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-316200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-203100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-132400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-147900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1606000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2398000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2161000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>434000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>446000</v>
+      </c>
+      <c r="I21" s="3">
         <v>2194000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2011000</v>
       </c>
-      <c r="I21" s="3">
-        <v>377000</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1603500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4870000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1777000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2014000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1344000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>272000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2233000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1015000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2098100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1110900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2964600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1053500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1685200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>503600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1221900</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E22" s="3">
         <v>164000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>155000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>133000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>131000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>73000</v>
       </c>
-      <c r="I22" s="3">
-        <v>81000</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>82000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3000</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1738,156 +1776,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>852000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1920000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1739000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>95000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3">
         <v>1734000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1591000</v>
       </c>
-      <c r="I23" s="3">
-        <v>-45000</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1129000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3102000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>929000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1146000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>518000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1464000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>717000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1968000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>497000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1447400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>526100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1778800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>456600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1088300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>74000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>821700</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E24" s="3">
         <v>531000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>430000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-19000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3">
         <v>416000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>379000</v>
       </c>
-      <c r="I24" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>248500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>650000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>201000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>387000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>112000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>375000</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>159000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>467000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>119000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-140000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>142900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>473200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>127900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>323100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>18800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1960,156 +2007,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>709000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1389000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1309000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>114000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3">
         <v>1318000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1212000</v>
       </c>
-      <c r="I26" s="3">
-        <v>-31000</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>880500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2452000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>728000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>759000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>406000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1089000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>558000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1501000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>378000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1587400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>383200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1305500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>328700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>765200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>55200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>631500</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>699000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1353000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1294000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>112000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3">
         <v>1300000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1197000</v>
       </c>
-      <c r="I27" s="3">
-        <v>-38000</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>904000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2451000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>698000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>719000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>403000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1076000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>551000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1497000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>378000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1570600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>373300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1275900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>313000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>760700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>54000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2182,8 +2238,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2206,47 +2265,47 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>11000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>271000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>87000</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>47000</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
         <v>42000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>1388000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>1083000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>915100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>28800</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>88900</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2256,8 +2315,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2330,8 +2392,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2404,156 +2469,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-135000</v>
+      </c>
+      <c r="E32" s="3">
         <v>27000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>14000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>13000</v>
       </c>
-      <c r="I32" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>222000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>96000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>353000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>246000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>533000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>79000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>478000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>95000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>131600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>146200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>316200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>203100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>132400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>147900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>54000</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>703000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1376000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1297000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>116000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3">
         <v>1306000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1199000</v>
       </c>
-      <c r="I33" s="3">
-        <v>-28000</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>884000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2722000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>785000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>719000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>403000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1123000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>593000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2885000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1461000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2485700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>402100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1364800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>313000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>760700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>54000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2626,161 +2700,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>703000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1376000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1297000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>116000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3">
         <v>1306000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1199000</v>
       </c>
-      <c r="I35" s="3">
-        <v>-28000</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>884000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2722000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>785000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>719000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>403000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1123000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>593000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2885000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1461000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2485700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>402100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1364800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>313000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>760700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>54000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43738</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43281</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42916</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42735</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42551</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42369</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42185</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2807,8 +2890,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2835,82 +2919,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3720000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2978000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3066000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3308000</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H41" s="3">
+        <v>6341000</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="3">
         <v>4275000</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5936000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5783000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6292000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7721000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14661000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9918000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1592000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9191000</v>
-      </c>
-      <c r="R41" s="3">
-        <v>1848000</v>
       </c>
       <c r="S41" s="3">
         <v>1848000</v>
       </c>
       <c r="T41" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="U41" s="3">
         <v>2530000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2137700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2689000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1564100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2825200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6149600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3829000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2983,526 +3071,550 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4820000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6422000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5893000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4798000</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H43" s="3">
+        <v>4507000</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>6450000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4300000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4611000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5335000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4122000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4946000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4253000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6008000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4682000</v>
-      </c>
-      <c r="R43" s="3">
-        <v>5091000</v>
       </c>
       <c r="S43" s="3">
         <v>5091000</v>
       </c>
       <c r="T43" s="3">
+        <v>5091000</v>
+      </c>
+      <c r="U43" s="3">
         <v>4539600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5396200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4373300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5548200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4467800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4211600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3121200</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4755000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4644000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4514000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4619000</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H44" s="3">
+        <v>4291000</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
         <v>4276000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4194000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3611000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3193000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3117000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2940000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3080000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3673000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3505000</v>
-      </c>
-      <c r="R44" s="3">
-        <v>3151000</v>
       </c>
       <c r="S44" s="3">
         <v>3151000</v>
       </c>
       <c r="T44" s="3">
+        <v>3151000</v>
+      </c>
+      <c r="U44" s="3">
         <v>3247700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3450200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3227000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3362600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3223500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2978000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2652800</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>446000</v>
+      </c>
+      <c r="E45" s="3">
         <v>371000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>428000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>626000</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H45" s="3">
+        <v>1461000</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>8000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>134000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>39000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17000</v>
-      </c>
-      <c r="R45" s="3">
-        <v>31000</v>
       </c>
       <c r="S45" s="3">
         <v>31000</v>
       </c>
       <c r="T45" s="3">
+        <v>31000</v>
+      </c>
+      <c r="U45" s="3">
         <v>1370800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>66500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>25300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>29200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>26900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>25800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>640900</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14083000</v>
+      </c>
+      <c r="E46" s="3">
         <v>14840000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15113000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13709000</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H46" s="3">
+        <v>16885000</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="3">
         <v>15009000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14833000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14044000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14855000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14977000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22574000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17258000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11283000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>17395000</v>
-      </c>
-      <c r="R46" s="3">
-        <v>10121000</v>
       </c>
       <c r="S46" s="3">
         <v>10121000</v>
       </c>
       <c r="T46" s="3">
+        <v>10121000</v>
+      </c>
+      <c r="U46" s="3">
         <v>11688100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11050500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10314600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10504100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10543300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13365000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10243800</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>737000</v>
+      </c>
+      <c r="E47" s="3">
         <v>929000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>484000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>609000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H47" s="3">
+        <v>620000</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>714000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>649000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>904000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>875000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>964000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1049000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1144000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1575000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1565000</v>
-      </c>
-      <c r="R47" s="3">
-        <v>1299000</v>
       </c>
       <c r="S47" s="3">
         <v>1299000</v>
       </c>
       <c r="T47" s="3">
+        <v>1299000</v>
+      </c>
+      <c r="U47" s="3">
         <v>1709400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1641500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1687600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1688600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1676300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1814700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1686800</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22726000</v>
+      </c>
+      <c r="E48" s="3">
         <v>22611000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20514000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20163000</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H48" s="3">
+        <v>19133000</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
         <v>19322000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>18943000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19502000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19100000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19317000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19099000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>39148000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>38153000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18046000</v>
-      </c>
-      <c r="R48" s="3">
-        <v>15607000</v>
       </c>
       <c r="S48" s="3">
         <v>15607000</v>
       </c>
       <c r="T48" s="3">
+        <v>15607000</v>
+      </c>
+      <c r="U48" s="3">
         <v>15663000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13744200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13933600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14146000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14655400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9181500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8712000</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12272000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12011000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11337000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11218000</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
+        <v>10199000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>10399000</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10287000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9848000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9468000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9373000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9378000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9475000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9702000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9656000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>8615000</v>
       </c>
       <c r="S49" s="3">
         <v>8615000</v>
       </c>
       <c r="T49" s="3">
+        <v>8615000</v>
+      </c>
+      <c r="U49" s="3">
         <v>8629400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8360200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8521600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8629200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8774000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5177700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4898300</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3575,8 +3687,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3649,82 +3764,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>795000</v>
+      </c>
+      <c r="E52" s="3">
         <v>830000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>657000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>634000</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H52" s="3">
+        <v>632000</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
         <v>456000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>607000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>372000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>231000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>313000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>275000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>161000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>166000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>115000</v>
-      </c>
-      <c r="R52" s="3">
-        <v>114000</v>
       </c>
       <c r="S52" s="3">
         <v>114000</v>
       </c>
       <c r="T52" s="3">
+        <v>114000</v>
+      </c>
+      <c r="U52" s="3">
         <v>149500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>200500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>232800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>362400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>262500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>253500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>302800</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3797,82 +3918,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>50613000</v>
+      </c>
+      <c r="E54" s="3">
         <v>51221000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>48105000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>46333000</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H54" s="3">
+        <v>47469000</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" s="3">
         <v>45983000</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>45319000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44670000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>44529000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44944000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>52375000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>47612000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>43034000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>46777000</v>
-      </c>
-      <c r="R54" s="3">
-        <v>35756000</v>
       </c>
       <c r="S54" s="3">
         <v>35756000</v>
       </c>
       <c r="T54" s="3">
+        <v>35756000</v>
+      </c>
+      <c r="U54" s="3">
         <v>37839400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34996800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34690200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35330300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35911500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29792500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>25843800</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3899,8 +4026,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3927,452 +4055,471 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3207000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2963000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3363000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2730000</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H57" s="3">
+        <v>3149000</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
         <v>7448000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2930000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5692000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6198000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4792000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5031000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4916000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5773000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5277000</v>
-      </c>
-      <c r="R57" s="3">
-        <v>5155000</v>
       </c>
       <c r="S57" s="3">
         <v>5155000</v>
       </c>
       <c r="T57" s="3">
+        <v>5155000</v>
+      </c>
+      <c r="U57" s="3">
         <v>5423600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5538000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5286900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5880300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5341800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4145900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3397000</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3331000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3549000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3477000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3247000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>2152000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>2490000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1751000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>846000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>452000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1553000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6185000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6920000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1571000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7213000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>1356000</v>
       </c>
       <c r="S58" s="3">
         <v>1356000</v>
       </c>
       <c r="T58" s="3">
+        <v>1356000</v>
+      </c>
+      <c r="U58" s="3">
         <v>378000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>463000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>302000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>720300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>848200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>412000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>524700</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1325000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1465000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1274000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1620000</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H59" s="3">
+        <v>2245000</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>1289000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1034000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1043000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1262000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1120000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1125000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1030000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1005000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>976000</v>
-      </c>
-      <c r="R59" s="3">
-        <v>984000</v>
       </c>
       <c r="S59" s="3">
         <v>984000</v>
       </c>
       <c r="T59" s="3">
+        <v>984000</v>
+      </c>
+      <c r="U59" s="3">
         <v>1412700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>898300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>887200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>880800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>955900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>322800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>617400</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10296000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10668000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10548000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9997000</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H60" s="3">
+        <v>10013000</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="3">
         <v>11227000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8041000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7581000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7912000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7465000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12341000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12866000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8349000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13466000</v>
-      </c>
-      <c r="R60" s="3">
-        <v>7495000</v>
       </c>
       <c r="S60" s="3">
         <v>7495000</v>
       </c>
       <c r="T60" s="3">
+        <v>7495000</v>
+      </c>
+      <c r="U60" s="3">
         <v>7214300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6899200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6476000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7481400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7146000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4880700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4539100</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12233000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11957000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11161000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10945000</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>10987000</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>8727000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9204000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11312000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11995000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10958000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15108000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10604000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11731000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9959000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>8557000</v>
       </c>
       <c r="S61" s="3">
         <v>8557000</v>
       </c>
       <c r="T61" s="3">
+        <v>8557000</v>
+      </c>
+      <c r="U61" s="3">
         <v>9162900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8838600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8251500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8908600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9497600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7241200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6360900</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1906000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2005000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1781000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1715000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H62" s="3">
+        <v>1856000</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
         <v>1470000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1877000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4863000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4550000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6173000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6000000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4507000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4543000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4400000</v>
-      </c>
-      <c r="R62" s="3">
-        <v>3733000</v>
       </c>
       <c r="S62" s="3">
         <v>3733000</v>
       </c>
       <c r="T62" s="3">
+        <v>3733000</v>
+      </c>
+      <c r="U62" s="3">
         <v>3546700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3845600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4104300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4229900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4071700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2946300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2973300</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4445,8 +4592,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4519,8 +4669,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4593,82 +4746,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27763000</v>
+      </c>
+      <c r="E66" s="3">
         <v>28055000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26654000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25591000</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H66" s="3">
+        <v>25848000</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" s="3">
         <v>24637000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>22279000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24437000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25152000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25288000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>34091000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28584000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25243000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28427000</v>
-      </c>
-      <c r="R66" s="3">
-        <v>20279000</v>
       </c>
       <c r="S66" s="3">
         <v>20279000</v>
       </c>
       <c r="T66" s="3">
+        <v>20279000</v>
+      </c>
+      <c r="U66" s="3">
         <v>20505300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>20143900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>19433500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>21220200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>21308800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15094000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13897900</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4695,8 +4854,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4769,8 +4929,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4843,8 +5006,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4858,13 +5024,13 @@
         <v>1000</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H70" s="3">
         <v>1000</v>
       </c>
       <c r="I70" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
         <v>1000</v>
@@ -4897,10 +5063,10 @@
         <v>1000</v>
       </c>
       <c r="T70" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U70" s="3">
         <v>1200</v>
-      </c>
-      <c r="U70" s="3">
-        <v>1100</v>
       </c>
       <c r="V70" s="3">
         <v>1100</v>
@@ -4912,13 +5078,16 @@
         <v>1100</v>
       </c>
       <c r="Y70" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="Z70" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4991,82 +5160,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>24036000</v>
+      </c>
+      <c r="E72" s="3">
         <v>23831000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>23030000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22346000</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H72" s="3">
+        <v>22918000</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3">
         <v>21712000</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22495000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20215000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19463000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12009000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11501000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11761000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11929000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12083000</v>
-      </c>
-      <c r="R72" s="3">
-        <v>9126000</v>
       </c>
       <c r="S72" s="3">
         <v>9126000</v>
       </c>
       <c r="T72" s="3">
+        <v>9126000</v>
+      </c>
+      <c r="U72" s="3">
         <v>9794500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7499600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7420300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6436900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6776800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6156600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6344400</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5139,8 +5314,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5213,8 +5391,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5287,82 +5468,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21606000</v>
+      </c>
+      <c r="E76" s="3">
         <v>21874000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20725000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20014000</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H76" s="3">
+        <v>20853000</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J76" s="3">
         <v>20694000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>22156000</v>
       </c>
-      <c r="J76" s="3">
-        <v>22156000</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20232000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19376000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19655000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18283000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19027000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17790000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18349000</v>
-      </c>
-      <c r="R76" s="3">
-        <v>15476000</v>
       </c>
       <c r="S76" s="3">
         <v>15476000</v>
       </c>
       <c r="T76" s="3">
+        <v>15476000</v>
+      </c>
+      <c r="U76" s="3">
         <v>17332900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14851800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15255600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14109000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14601600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14697300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11944700</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5435,161 +5622,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43738</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43281</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42916</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42735</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42551</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42369</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42185</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>703000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1376000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1297000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>116000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3">
         <v>1306000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1199000</v>
       </c>
-      <c r="I81" s="3">
-        <v>-28000</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>884000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2722000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>785000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>719000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>403000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1123000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>593000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2885000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1461000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2485700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>402100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1364800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>313000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>760700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>54000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5616,82 +5812,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
+        <v>402000</v>
+      </c>
+      <c r="F83" s="3">
         <v>401000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>384000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>339500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>339500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>397500</v>
       </c>
-      <c r="I83" s="3">
-        <v>397500</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>309500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1765000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>848000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>868000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>826000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3">
         <v>-445000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>265000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>518000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>650700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>584800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1185800</v>
-      </c>
-      <c r="W83" s="3">
-        <v>596900</v>
       </c>
       <c r="X83" s="3">
         <v>596900</v>
       </c>
       <c r="Y83" s="3">
+        <v>596900</v>
+      </c>
+      <c r="Z83" s="3">
         <v>429600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5764,8 +5964,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5838,8 +6041,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5912,8 +6118,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5986,8 +6195,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6060,82 +6272,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>1486000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1485000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-712000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>1631000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1634000</v>
       </c>
-      <c r="I89" s="3">
-        <v>-671000</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1589500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4210000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1565000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2930000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1008000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R89" s="3">
         <v>-1940000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>57000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-311000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2677100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-54300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2569300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>77400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2822900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-315800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1747800</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6162,82 +6380,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-505000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-624000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-506000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-404000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-439000</v>
       </c>
-      <c r="I91" s="3">
-        <v>-332000</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-463500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-967000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-587000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-482000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-514000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-656000</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3">
         <v>486000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-77000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-509000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-635200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-568200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-936600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-457800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-610400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-396700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-260600</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6310,8 +6532,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6384,82 +6609,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1788000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-521000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2096000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-759000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-478000</v>
       </c>
-      <c r="I94" s="3">
-        <v>-492000</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1521000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2546000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-519000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-613000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-447000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3">
         <v>1026000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1093000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1321000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2039500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1085400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-807000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-445400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-8485600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>301700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6486,82 +6717,86 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>238000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>481000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>750000</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>761000</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>92500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-906000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-729000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-170000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-537000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>96000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-52000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-358000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-116000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-412000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-386500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-260300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-161600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-275800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-135000</v>
       </c>
     </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6634,8 +6869,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6708,8 +6946,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6782,226 +7023,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-629000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-339000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-176000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>649000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1555000</v>
       </c>
-      <c r="I100" s="3">
-        <v>-191000</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-514500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3305000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2368000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4992000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5279000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3">
         <v>-544000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-456000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1337000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-311000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>667900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1901700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-859400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2637800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2125800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>610400</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="F101" s="3">
         <v>24000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>68000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-116500</v>
       </c>
-      <c r="I101" s="3">
-        <v>-116500</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-95000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-297000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-107000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>308000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>30000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
         <v>-11000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>178000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-81300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-103000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>63700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-33700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>170200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>132600</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-866000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>637000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3081000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>1447000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-375000</v>
       </c>
-      <c r="I102" s="3">
-        <v>-1286000</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-445000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1938000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1429000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2367000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5870000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R102" s="3">
         <v>-1158000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>525000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-287000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>245200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-574800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-75800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1261100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3052900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2281900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2522500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>CRH</t>
   </si>
@@ -656,354 +656,367 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43738</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42916</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42735</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42551</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42369</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42185</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6756000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8870000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10515000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9654000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6533000</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3">
         <v>10128000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9709000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8862500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>29206000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13167000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15372000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12215000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15285000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8583000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12847000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>27449000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11944000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11726300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13125100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>27218300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14241400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16005200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10998600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>12428300</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4919000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5710000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6456000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5979000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4726000</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3">
         <v>6365000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6079000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5832500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19379000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8867000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10060000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8365000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10130000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
         <v>8729000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18391000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8236000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7398500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8960500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>18189500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9780400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>10894500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7845700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8641600</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1837000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3160000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4059000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3675000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1807000</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3">
         <v>3763000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3630000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3030000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9827000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4300000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5312000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3850000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5155000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>4118000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9058000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3708000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4327900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4164600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9028900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4461000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5110700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3152900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3786700</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1031,8 +1044,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1108,8 +1122,11 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1185,71 +1202,74 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E14" s="3">
         <v>115000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-120000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-121000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-148000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>-11000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-18000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>45500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>25000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>2000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>21000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>5500</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1262,43 +1282,46 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E15" s="3">
         <v>510000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>467000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>424000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>397000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>446000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>402000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>401000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>376000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>46000</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1339,8 +1362,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1365,162 +1391,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6743000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7639000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8611000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7922000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6492000</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3">
         <v>8350000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8112000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7641000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25879000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12142000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13873000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11451000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13288000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3">
         <v>12051000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>25003000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11352000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10147400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12452700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>25123300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13581700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14784500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10776700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>11552600</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1231000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1904000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1732000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>41000</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3">
         <v>1778000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1597000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1221500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3327000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1025000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1499000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>764000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1997000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>796000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2446000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>592000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1579000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>672300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2095000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>659700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1220700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>221900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>875700</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1548,197 +1581,204 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E20" s="3">
         <v>135000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-27000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5000</v>
       </c>
-      <c r="G20" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="H20" s="3">
+        <v>-156000</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
         <v>-14000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-13000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-222000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-96000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-353000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-246000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-533000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="3">
         <v>-79000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-478000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-95000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-131600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-146200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-316200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-203100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-132400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-147900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>454000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1606000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2398000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2161000</v>
       </c>
-      <c r="G21" s="3">
-        <v>434000</v>
-      </c>
       <c r="H21" s="3">
+        <v>594000</v>
+      </c>
+      <c r="I21" s="3">
         <v>446000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2194000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2011000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1603500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4870000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1777000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2014000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1344000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>272000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2233000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1015000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2098100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1110900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2964600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1053500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1685200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>503600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1221900</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E22" s="3">
         <v>160000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>164000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>155000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>133000</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3">
         <v>131000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>73000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>82000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1779,162 +1819,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-156000</v>
+      </c>
+      <c r="E23" s="3">
         <v>852000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1920000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1739000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>95000</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3">
         <v>1734000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1591000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1129000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3102000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>929000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1146000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>518000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1464000</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="3">
         <v>717000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1968000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>497000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1447400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>526100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1778800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>456600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1088300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>74000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>821700</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="E24" s="3">
         <v>143000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>531000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>430000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-19000</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3">
         <v>416000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>379000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>248500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>650000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>201000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>387000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>112000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>375000</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="3">
         <v>159000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>467000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>119000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-140000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>142900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>473200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>127900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>323100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>18800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2010,162 +2059,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="E26" s="3">
         <v>709000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1389000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1309000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>114000</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3">
         <v>1318000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1212000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>880500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2452000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>728000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>759000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>406000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1089000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="3">
         <v>558000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1501000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>378000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1587400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>383200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1305500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>328700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>765200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>55200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>631500</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="E27" s="3">
         <v>699000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1353000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1294000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>112000</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3">
         <v>1300000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1197000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>904000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2451000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>698000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>719000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>403000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1076000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="3">
         <v>551000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1497000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>378000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1570600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>373300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1275900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>313000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>760700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>54000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2241,8 +2299,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2268,47 +2329,47 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>11000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>271000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>87000</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>47000</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
         <v>42000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>1388000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>1083000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>915100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>28800</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>88900</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2318,8 +2379,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2395,8 +2459,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2472,162 +2539,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-135000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>27000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="H32" s="3">
+        <v>156000</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
         <v>14000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>13000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>222000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>96000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>353000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>246000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>533000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="3">
         <v>79000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>478000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>95000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>131600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>146200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>316200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>203100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>132400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>147900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>54000</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="E33" s="3">
         <v>703000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1376000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1297000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>116000</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3">
         <v>1306000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1199000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>884000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2722000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>785000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>719000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>403000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1123000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="3">
         <v>593000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2885000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1461000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2485700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>402100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1364800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>313000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>760700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>54000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2703,167 +2779,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="E35" s="3">
         <v>703000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1376000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1297000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>116000</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3">
         <v>1306000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1199000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>884000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2722000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>785000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>719000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>403000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1123000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S35" s="3">
         <v>593000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2885000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1461000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2485700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>402100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1364800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>313000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>760700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>54000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43738</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42916</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42735</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42551</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42369</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42185</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2891,8 +2976,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2920,85 +3006,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3352000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3720000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2978000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3066000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3308000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6341000</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" s="3">
         <v>4275000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5936000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5783000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6292000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7721000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14661000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9918000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1592000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9191000</v>
-      </c>
-      <c r="S41" s="3">
-        <v>1848000</v>
       </c>
       <c r="T41" s="3">
         <v>1848000</v>
       </c>
       <c r="U41" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="V41" s="3">
         <v>2530000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2137700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2689000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1564100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2825200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6149600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3829000</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3074,547 +3164,571 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5493000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4820000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6422000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5893000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4798000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4507000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>6450000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4300000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4611000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5335000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4122000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4946000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4253000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6008000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4682000</v>
-      </c>
-      <c r="S43" s="3">
-        <v>5091000</v>
       </c>
       <c r="T43" s="3">
         <v>5091000</v>
       </c>
       <c r="U43" s="3">
+        <v>5091000</v>
+      </c>
+      <c r="V43" s="3">
         <v>4539600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5396200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4373300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5548200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4467800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4211600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3121200</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4960000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4755000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4644000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4514000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4619000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4291000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
         <v>4276000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4194000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3611000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3193000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3117000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2940000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3080000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3673000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3505000</v>
-      </c>
-      <c r="S44" s="3">
-        <v>3151000</v>
       </c>
       <c r="T44" s="3">
         <v>3151000</v>
       </c>
       <c r="U44" s="3">
+        <v>3151000</v>
+      </c>
+      <c r="V44" s="3">
         <v>3247700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3450200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3227000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3362600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3223500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2978000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2652800</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E45" s="3">
         <v>446000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>371000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>428000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>626000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1461000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>8000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>134000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>39000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>35000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17000</v>
-      </c>
-      <c r="S45" s="3">
-        <v>31000</v>
       </c>
       <c r="T45" s="3">
         <v>31000</v>
       </c>
       <c r="U45" s="3">
+        <v>31000</v>
+      </c>
+      <c r="V45" s="3">
         <v>1370800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>66500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>25300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>29200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>26900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>25800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>640900</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14242000</v>
+      </c>
+      <c r="E46" s="3">
         <v>14083000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14840000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15113000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13709000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16885000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="3">
         <v>15009000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14833000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14044000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14855000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14977000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22574000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>17258000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11283000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>17395000</v>
-      </c>
-      <c r="S46" s="3">
-        <v>10121000</v>
       </c>
       <c r="T46" s="3">
         <v>10121000</v>
       </c>
       <c r="U46" s="3">
+        <v>10121000</v>
+      </c>
+      <c r="V46" s="3">
         <v>11688100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11050500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10314600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10504100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10543300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>13365000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10243800</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>732000</v>
+      </c>
+      <c r="E47" s="3">
         <v>737000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>929000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>484000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>609000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>620000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>714000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>649000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>904000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>875000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>964000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1049000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1144000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1575000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1565000</v>
-      </c>
-      <c r="S47" s="3">
-        <v>1299000</v>
       </c>
       <c r="T47" s="3">
         <v>1299000</v>
       </c>
       <c r="U47" s="3">
+        <v>1299000</v>
+      </c>
+      <c r="V47" s="3">
         <v>1709400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1641500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1687600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1688600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1676300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1814700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1686800</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23451000</v>
+      </c>
+      <c r="E48" s="3">
         <v>22726000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22611000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20514000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20163000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19133000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="3">
         <v>19322000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18943000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19502000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19100000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19317000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19099000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>39148000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>38153000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>18046000</v>
-      </c>
-      <c r="S48" s="3">
-        <v>15607000</v>
       </c>
       <c r="T48" s="3">
         <v>15607000</v>
       </c>
       <c r="U48" s="3">
+        <v>15607000</v>
+      </c>
+      <c r="V48" s="3">
         <v>15663000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13744200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13933600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14146000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14655400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9181500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8712000</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12683000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12272000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12011000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11337000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11218000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10199000</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>10399000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10287000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9848000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9468000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9373000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9378000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9475000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9702000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9656000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>8615000</v>
       </c>
       <c r="T49" s="3">
         <v>8615000</v>
       </c>
       <c r="U49" s="3">
+        <v>8615000</v>
+      </c>
+      <c r="V49" s="3">
         <v>8629400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8360200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8521600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8629200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8774000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5177700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4898300</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3690,8 +3804,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3767,85 +3884,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>813000</v>
+      </c>
+      <c r="E52" s="3">
         <v>795000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>830000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>657000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>634000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>632000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>456000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>607000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>372000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>231000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>313000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>275000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>161000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>166000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>115000</v>
-      </c>
-      <c r="S52" s="3">
-        <v>114000</v>
       </c>
       <c r="T52" s="3">
         <v>114000</v>
       </c>
       <c r="U52" s="3">
+        <v>114000</v>
+      </c>
+      <c r="V52" s="3">
         <v>149500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>200500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>232800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>362400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>262500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>253500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>302800</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3921,85 +4044,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>51921000</v>
+      </c>
+      <c r="E54" s="3">
         <v>50613000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>51221000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>48105000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>46333000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>47469000</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" s="3">
         <v>45983000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>45319000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>44670000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44529000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>44944000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>52375000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>47612000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>43034000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>46777000</v>
-      </c>
-      <c r="S54" s="3">
-        <v>35756000</v>
       </c>
       <c r="T54" s="3">
         <v>35756000</v>
       </c>
       <c r="U54" s="3">
+        <v>35756000</v>
+      </c>
+      <c r="V54" s="3">
         <v>37839400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34996800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34690200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35330300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35911500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>29792500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>25843800</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4027,8 +4156,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4056,470 +4186,489 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2777000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3207000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2963000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3363000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2730000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3149000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>7448000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2930000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5692000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6198000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4792000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5031000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4916000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5773000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5277000</v>
-      </c>
-      <c r="S57" s="3">
-        <v>5155000</v>
       </c>
       <c r="T57" s="3">
         <v>5155000</v>
       </c>
       <c r="U57" s="3">
+        <v>5155000</v>
+      </c>
+      <c r="V57" s="3">
         <v>5423600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5538000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5286900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5880300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5341800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4145900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3397000</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1705000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3331000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3549000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3477000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3247000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2152000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>2490000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1751000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>846000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>452000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1553000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6185000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6920000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1571000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7213000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>1356000</v>
       </c>
       <c r="T58" s="3">
         <v>1356000</v>
       </c>
       <c r="U58" s="3">
+        <v>1356000</v>
+      </c>
+      <c r="V58" s="3">
         <v>378000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>463000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>302000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>720300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>848200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>412000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>524700</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1770000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1325000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1465000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1274000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1620000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2245000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>1289000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1034000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1043000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1262000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1120000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1125000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1030000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1005000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>976000</v>
-      </c>
-      <c r="S59" s="3">
-        <v>984000</v>
       </c>
       <c r="T59" s="3">
         <v>984000</v>
       </c>
       <c r="U59" s="3">
+        <v>984000</v>
+      </c>
+      <c r="V59" s="3">
         <v>1412700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>898300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>887200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>880800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>955900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>322800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>617400</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8712000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10296000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10668000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10548000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9997000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10013000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" s="3">
         <v>11227000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8041000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7581000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7912000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7465000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12341000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12866000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8349000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13466000</v>
-      </c>
-      <c r="S60" s="3">
-        <v>7495000</v>
       </c>
       <c r="T60" s="3">
         <v>7495000</v>
       </c>
       <c r="U60" s="3">
+        <v>7495000</v>
+      </c>
+      <c r="V60" s="3">
         <v>7214300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6899200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6476000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7481400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7146000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4880700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4539100</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15624000</v>
+      </c>
+      <c r="E61" s="3">
         <v>12233000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11957000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11161000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10945000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10987000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>8727000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9204000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11312000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11995000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10958000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15108000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10604000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11731000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9959000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>8557000</v>
       </c>
       <c r="T61" s="3">
         <v>8557000</v>
       </c>
       <c r="U61" s="3">
+        <v>8557000</v>
+      </c>
+      <c r="V61" s="3">
         <v>9162900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8838600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8251500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8908600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9497600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7241200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6360900</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1858000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1906000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2005000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1781000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1715000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1856000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>1470000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1877000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4863000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4550000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6173000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6000000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4507000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4543000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4400000</v>
-      </c>
-      <c r="S62" s="3">
-        <v>3733000</v>
       </c>
       <c r="T62" s="3">
         <v>3733000</v>
       </c>
       <c r="U62" s="3">
+        <v>3733000</v>
+      </c>
+      <c r="V62" s="3">
         <v>3546700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3845600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4104300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4229900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4071700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2946300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2973300</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4595,8 +4744,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4672,8 +4824,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4749,85 +4904,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>29564000</v>
+      </c>
+      <c r="E66" s="3">
         <v>27763000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>28055000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26654000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25591000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25848000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" s="3">
         <v>24637000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22279000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24437000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25152000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25288000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>34091000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28584000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25243000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28427000</v>
-      </c>
-      <c r="S66" s="3">
-        <v>20279000</v>
       </c>
       <c r="T66" s="3">
         <v>20279000</v>
       </c>
       <c r="U66" s="3">
+        <v>20279000</v>
+      </c>
+      <c r="V66" s="3">
         <v>20505300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>20143900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19433500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>21220200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>21308800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15094000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13897900</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4855,8 +5016,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4932,8 +5094,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5009,8 +5174,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5030,10 +5198,10 @@
         <v>1000</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J70" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>1000</v>
@@ -5066,10 +5234,10 @@
         <v>1000</v>
       </c>
       <c r="U70" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V70" s="3">
         <v>1200</v>
-      </c>
-      <c r="V70" s="3">
-        <v>1100</v>
       </c>
       <c r="W70" s="3">
         <v>1100</v>
@@ -5081,13 +5249,16 @@
         <v>1100</v>
       </c>
       <c r="Z70" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AA70" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5163,85 +5334,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>23375000</v>
+      </c>
+      <c r="E72" s="3">
         <v>24036000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>23831000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>23030000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22346000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>22918000</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
         <v>21712000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22495000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20215000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19463000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12009000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11501000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11761000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11929000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12083000</v>
-      </c>
-      <c r="S72" s="3">
-        <v>9126000</v>
       </c>
       <c r="T72" s="3">
         <v>9126000</v>
       </c>
       <c r="U72" s="3">
+        <v>9126000</v>
+      </c>
+      <c r="V72" s="3">
         <v>9794500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7499600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7420300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6436900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6776800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6156600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6344400</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5317,8 +5494,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5394,8 +5574,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5471,85 +5654,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21118000</v>
+      </c>
+      <c r="E76" s="3">
         <v>21606000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21874000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20725000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20014000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20853000</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K76" s="3">
         <v>20694000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22156000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20232000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19376000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19655000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18283000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19027000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17790000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18349000</v>
-      </c>
-      <c r="S76" s="3">
-        <v>15476000</v>
       </c>
       <c r="T76" s="3">
         <v>15476000</v>
       </c>
       <c r="U76" s="3">
+        <v>15476000</v>
+      </c>
+      <c r="V76" s="3">
         <v>17332900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14851800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15255600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14109000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14601600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14697300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11944700</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5625,167 +5814,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43738</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42916</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42735</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42551</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42369</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42185</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="E81" s="3">
         <v>703000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1376000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1297000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>116000</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3">
         <v>1306000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1199000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>884000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2722000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>785000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>719000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>403000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1123000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S81" s="3">
         <v>593000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2885000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1461000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2485700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>402100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1364800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>313000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>760700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>54000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5813,85 +6011,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>402000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>401000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>384000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>339500</v>
       </c>
       <c r="I83" s="3">
         <v>339500</v>
       </c>
       <c r="J83" s="3">
+        <v>339500</v>
+      </c>
+      <c r="K83" s="3">
         <v>397500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>309500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1765000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>848000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>868000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>826000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3">
         <v>-445000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>265000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>518000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>650700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>584800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1185800</v>
-      </c>
-      <c r="X83" s="3">
-        <v>596900</v>
       </c>
       <c r="Y83" s="3">
         <v>596900</v>
       </c>
       <c r="Z83" s="3">
+        <v>596900</v>
+      </c>
+      <c r="AA83" s="3">
         <v>429600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5967,8 +6169,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6044,8 +6249,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6121,8 +6329,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6198,8 +6409,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6275,85 +6489,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3">
+        <v>-659000</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
         <v>1486000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1485000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-712000</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
         <v>1631000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1634000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1589500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4210000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1565000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2930000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1008000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S89" s="3">
         <v>-1940000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>57000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-311000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2677100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-54300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2569300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>77400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2822900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-315800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1747800</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6381,85 +6601,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3">
+        <v>-645000</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>-505000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-624000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-506000</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
         <v>-404000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-439000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-463500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-967000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-587000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-482000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-514000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-656000</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S91" s="3">
         <v>486000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-77000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-509000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-635200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-568200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-936600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-457800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-610400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-396700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-260600</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6535,8 +6759,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6612,85 +6839,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3">
+        <v>-964000</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1788000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-521000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2096000</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3">
         <v>-759000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-478000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1521000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2546000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-519000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-613000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-447000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S94" s="3">
         <v>1026000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1093000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1321000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2039500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1085400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-807000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-445400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8485600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>301700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6718,85 +6951,89 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>238000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>481000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>750000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>761000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>92500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-906000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-729000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-170000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-537000</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>96000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-52000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-358000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-116000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-412000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-386500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-260300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-161600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-275800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-135000</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6872,8 +7109,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6949,8 +7189,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7026,235 +7269,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3">
+        <v>1141000</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
         <v>-629000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-339000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-176000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
         <v>649000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1555000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-514500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3305000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2368000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4992000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5279000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S100" s="3">
         <v>-544000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-456000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1337000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-311000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>667900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1901700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-859400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2637800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2125800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>610400</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="D101" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3">
         <v>-74000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>24000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>68000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>1000</v>
       </c>
       <c r="I101" s="3">
         <v>1000</v>
       </c>
       <c r="J101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-116500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-95000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-297000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-107000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>308000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>30000</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3">
         <v>-11000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>178000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>8000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-81300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-103000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>63700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-33700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>170200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>132600</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-407000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-866000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>637000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3081000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>1447000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-375000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-445000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1938000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1429000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2367000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5870000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S102" s="3">
         <v>-1158000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>525000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-287000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>245200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-574800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-75800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1261100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3052900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2281900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2522500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>CRH</t>
   </si>
@@ -656,367 +656,380 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42916</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42735</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42551</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42369</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42185</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10206000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6756000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8870000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10515000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9654000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6533000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>10128000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9709000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8862500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>29206000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13167000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15372000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12215000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15285000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8583000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12847000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>27449000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11944000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11726300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13125100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>27218300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14241400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16005200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10998600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12428300</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6180000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4919000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5710000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6456000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5979000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4726000</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>6365000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6079000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5832500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19379000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8867000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10060000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8365000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10130000</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T9" s="3">
         <v>8729000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>18391000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8236000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7398500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8960500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>18189500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9780400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>10894500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7845700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8641600</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4026000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1837000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3160000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4059000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3675000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1807000</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>3763000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3630000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3030000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9827000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4300000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5312000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3850000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5155000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T10" s="3">
         <v>4118000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9058000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3708000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4327900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4164600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9028900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4461000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5110700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3152900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3786700</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1045,8 +1058,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1139,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1205,74 +1222,77 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-9000</v>
+        <v>-3000</v>
       </c>
       <c r="E14" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F14" s="3">
         <v>115000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-120000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-121000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="L14" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="M14" s="3">
+        <v>45500</v>
+      </c>
+      <c r="N14" s="3">
+        <v>25000</v>
+      </c>
+      <c r="O14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U14" s="3">
+        <v>21000</v>
+      </c>
+      <c r="V14" s="3">
         <v>12000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-18000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>45500</v>
-      </c>
-      <c r="M14" s="3">
-        <v>25000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="P14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
-        <v>2000</v>
-      </c>
-      <c r="T14" s="3">
-        <v>21000</v>
-      </c>
-      <c r="U14" s="3">
-        <v>12000</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>5500</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1285,46 +1305,49 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>528000</v>
+      </c>
+      <c r="E15" s="3">
         <v>477000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>510000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>467000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>424000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>397000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>446000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>402000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>401000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>376000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>46000</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1365,8 +1388,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1392,168 +1418,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8285000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6743000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7639000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8611000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7922000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6492000</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>8350000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8112000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7641000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25879000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12142000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13873000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11451000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13288000</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T17" s="3">
         <v>12051000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25003000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11352000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10147400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12452700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>25123300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13581700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14784500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10776700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>11552600</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="E18" s="3">
         <v>13000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1231000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1904000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1732000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>41000</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>1778000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1597000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1221500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3327000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1025000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1499000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>764000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1997000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T18" s="3">
         <v>796000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2446000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>592000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1579000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>672300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2095000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>659700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1220700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>221900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>875700</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1582,206 +1615,213 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>36000</v>
+        <v>-1000</v>
       </c>
       <c r="E20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F20" s="3">
         <v>135000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-27000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-156000</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="I20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-14000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-13000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-222000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-96000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-353000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-246000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-533000</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T20" s="3">
         <v>-79000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-478000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-95000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-131600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-146200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-316200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-203100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-132400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-147900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>454000</v>
+        <v>2450000</v>
       </c>
       <c r="E21" s="3">
+        <v>480000</v>
+      </c>
+      <c r="F21" s="3">
         <v>1606000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2398000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2161000</v>
       </c>
-      <c r="H21" s="3">
-        <v>594000</v>
-      </c>
       <c r="I21" s="3">
+        <v>434000</v>
+      </c>
+      <c r="J21" s="3">
         <v>446000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2194000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2011000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1603500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4870000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1777000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2014000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1344000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3">
         <v>272000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2233000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1015000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2098100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1110900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2964600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1053500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1685200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>503600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1221900</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E22" s="3">
         <v>181000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>160000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>164000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>155000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>133000</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>131000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>73000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>82000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3000</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1822,168 +1862,177 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1757000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-156000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>852000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1920000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1739000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>95000</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>1734000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1591000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1129000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3102000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>929000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1146000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>518000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1464000</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T23" s="3">
         <v>717000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1968000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>497000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1447400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>526100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1778800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>456600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1088300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>74000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>821700</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>425000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-58000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>143000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>531000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>430000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-19000</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>416000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>379000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>248500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>650000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>201000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>387000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>112000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>375000</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T24" s="3">
         <v>159000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>467000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>119000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-140000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>142900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>473200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>127900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>323100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>18800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2062,168 +2111,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-98000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>709000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1389000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1309000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>114000</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>1318000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1212000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>880500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2452000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>728000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>759000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>406000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1089000</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T26" s="3">
         <v>558000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1501000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>378000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1587400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>383200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1305500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>328700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>765200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>55200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>631500</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1313000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-101000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>699000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1353000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1294000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>112000</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>1300000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1197000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>904000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2451000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>698000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>719000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>403000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1076000</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T27" s="3">
         <v>551000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1497000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>378000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1570600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>373300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1275900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>313000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>760700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>54000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2302,8 +2360,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2332,47 +2393,47 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>11000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>271000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>87000</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>47000</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
         <v>42000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>1388000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>1083000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>915100</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>28800</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>88900</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2382,8 +2443,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2462,8 +2526,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2542,168 +2609,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-36000</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-135000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>27000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5000</v>
       </c>
-      <c r="H32" s="3">
-        <v>156000</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="I32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>14000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>13000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>222000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>96000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>353000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>246000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>533000</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T32" s="3">
         <v>79000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>478000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>95000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>131600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>146200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>316200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>203100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>132400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>147900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>54000</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1319000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-94000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>703000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1376000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1297000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>116000</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>1306000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1199000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>884000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2722000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>785000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>719000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>403000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1123000</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T33" s="3">
         <v>593000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2885000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1461000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2485700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>402100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1364800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>313000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>760700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>54000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2782,173 +2858,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1319000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-94000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>703000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1376000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1297000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>116000</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>1306000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1199000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>884000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2722000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>785000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>719000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>403000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1123000</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T35" s="3">
         <v>593000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2885000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1461000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2485700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>402100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1364800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>313000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>760700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>54000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42916</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42735</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42551</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42369</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42185</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2977,8 +3062,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3007,88 +3093,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2876000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3352000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3720000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2978000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3066000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3308000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6341000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L41" s="3">
         <v>4275000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5936000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5783000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6292000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7721000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14661000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9918000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1592000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9191000</v>
-      </c>
-      <c r="T41" s="3">
-        <v>1848000</v>
       </c>
       <c r="U41" s="3">
         <v>1848000</v>
       </c>
       <c r="V41" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="W41" s="3">
         <v>2530000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2137700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2689000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1564100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2825200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6149600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3829000</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3167,568 +3257,592 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6704000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5493000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4820000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6422000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5893000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4798000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4507000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3">
         <v>6450000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4300000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4611000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5335000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4122000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4946000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4253000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6008000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4682000</v>
-      </c>
-      <c r="T43" s="3">
-        <v>5091000</v>
       </c>
       <c r="U43" s="3">
         <v>5091000</v>
       </c>
       <c r="V43" s="3">
+        <v>5091000</v>
+      </c>
+      <c r="W43" s="3">
         <v>4539600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5396200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4373300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5548200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4467800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4211600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3121200</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5051000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4960000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4755000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4644000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4514000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4619000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4291000</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3">
         <v>4276000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4194000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3611000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3193000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3117000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2940000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3080000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3673000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3505000</v>
-      </c>
-      <c r="T44" s="3">
-        <v>3151000</v>
       </c>
       <c r="U44" s="3">
         <v>3151000</v>
       </c>
       <c r="V44" s="3">
+        <v>3151000</v>
+      </c>
+      <c r="W44" s="3">
         <v>3247700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3450200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3227000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3362600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3223500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2978000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2652800</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E45" s="3">
         <v>46000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>446000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>371000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>428000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>626000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1461000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>8000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>134000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>39000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>35000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17000</v>
-      </c>
-      <c r="T45" s="3">
-        <v>31000</v>
       </c>
       <c r="U45" s="3">
         <v>31000</v>
       </c>
       <c r="V45" s="3">
+        <v>31000</v>
+      </c>
+      <c r="W45" s="3">
         <v>1370800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>66500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>25300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>29200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>26900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>25800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>640900</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15151000</v>
+      </c>
+      <c r="E46" s="3">
         <v>14242000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14083000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14840000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15113000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13709000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16885000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L46" s="3">
         <v>15009000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14833000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14044000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14855000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14977000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22574000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>17258000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11283000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17395000</v>
-      </c>
-      <c r="T46" s="3">
-        <v>10121000</v>
       </c>
       <c r="U46" s="3">
         <v>10121000</v>
       </c>
       <c r="V46" s="3">
+        <v>10121000</v>
+      </c>
+      <c r="W46" s="3">
         <v>11688100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11050500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10314600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10504100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10543300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>13365000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10243800</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>712000</v>
+      </c>
+      <c r="E47" s="3">
         <v>732000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>737000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>929000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>484000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>609000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>620000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>714000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>649000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>904000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>875000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>964000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1049000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1144000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1575000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1565000</v>
-      </c>
-      <c r="T47" s="3">
-        <v>1299000</v>
       </c>
       <c r="U47" s="3">
         <v>1299000</v>
       </c>
       <c r="V47" s="3">
+        <v>1299000</v>
+      </c>
+      <c r="W47" s="3">
         <v>1709400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1641500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1687600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1688600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1676300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1814700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1686800</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24312000</v>
+      </c>
+      <c r="E48" s="3">
         <v>23451000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22726000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22611000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20514000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20163000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19133000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L48" s="3">
         <v>19322000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18943000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19502000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19100000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19317000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19099000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>39148000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>38153000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18046000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>15607000</v>
       </c>
       <c r="U48" s="3">
         <v>15607000</v>
       </c>
       <c r="V48" s="3">
+        <v>15607000</v>
+      </c>
+      <c r="W48" s="3">
         <v>15663000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13744200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13933600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14146000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14655400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9181500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8712000</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12912000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12683000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12272000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12011000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11337000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11218000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10199000</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>10399000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10287000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9848000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9468000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9373000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9378000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9475000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9702000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9656000</v>
-      </c>
-      <c r="T49" s="3">
-        <v>8615000</v>
       </c>
       <c r="U49" s="3">
         <v>8615000</v>
       </c>
       <c r="V49" s="3">
+        <v>8615000</v>
+      </c>
+      <c r="W49" s="3">
         <v>8629400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8360200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8521600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8629200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8774000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5177700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4898300</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3807,8 +3921,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3887,88 +4004,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>897000</v>
+      </c>
+      <c r="E52" s="3">
         <v>813000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>795000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>830000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>657000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>634000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>632000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>456000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>607000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>372000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>231000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>313000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>275000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>161000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>166000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>115000</v>
-      </c>
-      <c r="T52" s="3">
-        <v>114000</v>
       </c>
       <c r="U52" s="3">
         <v>114000</v>
       </c>
       <c r="V52" s="3">
+        <v>114000</v>
+      </c>
+      <c r="W52" s="3">
         <v>149500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>200500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>232800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>362400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>262500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>253500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>302800</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4047,88 +4170,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>53984000</v>
+      </c>
+      <c r="E54" s="3">
         <v>51921000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>50613000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>51221000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48105000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>46333000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>47469000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L54" s="3">
         <v>45983000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>45319000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44670000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>44529000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>44944000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>52375000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>47612000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>43034000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>46777000</v>
-      </c>
-      <c r="T54" s="3">
-        <v>35756000</v>
       </c>
       <c r="U54" s="3">
         <v>35756000</v>
       </c>
       <c r="V54" s="3">
+        <v>35756000</v>
+      </c>
+      <c r="W54" s="3">
         <v>37839400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34996800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34690200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35330300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>35911500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>29792500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>25843800</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4157,8 +4286,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4187,488 +4317,507 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3303000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2777000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3207000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2963000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3363000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2730000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3149000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3">
         <v>7448000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2930000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5692000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6198000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4792000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5031000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4916000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5773000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5277000</v>
-      </c>
-      <c r="T57" s="3">
-        <v>5155000</v>
       </c>
       <c r="U57" s="3">
         <v>5155000</v>
       </c>
       <c r="V57" s="3">
+        <v>5155000</v>
+      </c>
+      <c r="W57" s="3">
         <v>5423600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5538000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5286900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5880300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5341800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4145900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3397000</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1418000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1705000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3331000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3549000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3477000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3247000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2152000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>2490000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1751000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>846000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>452000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1553000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6185000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6920000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1571000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7213000</v>
-      </c>
-      <c r="T58" s="3">
-        <v>1356000</v>
       </c>
       <c r="U58" s="3">
         <v>1356000</v>
       </c>
       <c r="V58" s="3">
+        <v>1356000</v>
+      </c>
+      <c r="W58" s="3">
         <v>378000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>463000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>302000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>720300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>848200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>412000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>524700</v>
       </c>
     </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1513000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1770000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1325000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1465000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1274000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1620000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2245000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>1289000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1034000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1043000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1262000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1120000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1125000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1030000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1005000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>976000</v>
-      </c>
-      <c r="T59" s="3">
-        <v>984000</v>
       </c>
       <c r="U59" s="3">
         <v>984000</v>
       </c>
       <c r="V59" s="3">
+        <v>984000</v>
+      </c>
+      <c r="W59" s="3">
         <v>1412700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>898300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>887200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>880800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>955900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>322800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>617400</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8684000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8712000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10296000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10668000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10548000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9997000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10013000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L60" s="3">
         <v>11227000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8041000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7581000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7912000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7465000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12341000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12866000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8349000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13466000</v>
-      </c>
-      <c r="T60" s="3">
-        <v>7495000</v>
       </c>
       <c r="U60" s="3">
         <v>7495000</v>
       </c>
       <c r="V60" s="3">
+        <v>7495000</v>
+      </c>
+      <c r="W60" s="3">
         <v>7214300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6899200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6476000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7481400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7146000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4880700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4539100</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16180000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15624000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12233000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11957000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11161000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10945000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10987000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>8727000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9204000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11312000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11995000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10958000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15108000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10604000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11731000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9959000</v>
-      </c>
-      <c r="T61" s="3">
-        <v>8557000</v>
       </c>
       <c r="U61" s="3">
         <v>8557000</v>
       </c>
       <c r="V61" s="3">
+        <v>8557000</v>
+      </c>
+      <c r="W61" s="3">
         <v>9162900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8838600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>8251500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8908600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>9497600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7241200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6360900</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2050000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1858000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1906000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2005000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1781000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1715000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1856000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>1470000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1877000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4863000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4550000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6173000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6000000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4507000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4543000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4400000</v>
-      </c>
-      <c r="T62" s="3">
-        <v>3733000</v>
       </c>
       <c r="U62" s="3">
         <v>3733000</v>
       </c>
       <c r="V62" s="3">
+        <v>3733000</v>
+      </c>
+      <c r="W62" s="3">
         <v>3546700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3845600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4104300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4229900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4071700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2946300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2973300</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4747,8 +4896,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4827,8 +4979,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4907,88 +5062,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>30354000</v>
+      </c>
+      <c r="E66" s="3">
         <v>29564000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27763000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>28055000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26654000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25591000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25848000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L66" s="3">
         <v>24637000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22279000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24437000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25152000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25288000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>34091000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28584000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25243000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28427000</v>
-      </c>
-      <c r="T66" s="3">
-        <v>20279000</v>
       </c>
       <c r="U66" s="3">
         <v>20279000</v>
       </c>
       <c r="V66" s="3">
+        <v>20279000</v>
+      </c>
+      <c r="W66" s="3">
         <v>20505300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>20143900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19433500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>21220200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>21308800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15094000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13897900</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5017,8 +5178,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5097,8 +5259,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5177,8 +5342,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5201,10 +5369,10 @@
         <v>1000</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K70" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L70" s="3">
         <v>1000</v>
@@ -5237,10 +5405,10 @@
         <v>1000</v>
       </c>
       <c r="V70" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W70" s="3">
         <v>1200</v>
-      </c>
-      <c r="W70" s="3">
-        <v>1100</v>
       </c>
       <c r="X70" s="3">
         <v>1100</v>
@@ -5252,13 +5420,16 @@
         <v>1100</v>
       </c>
       <c r="AA70" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AB70" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5337,88 +5508,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>24106000</v>
+      </c>
+      <c r="E72" s="3">
         <v>23375000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>24036000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>23831000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>23030000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>22346000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>22918000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>21712000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22495000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20215000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19463000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12009000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11501000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11761000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>11929000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12083000</v>
-      </c>
-      <c r="T72" s="3">
-        <v>9126000</v>
       </c>
       <c r="U72" s="3">
         <v>9126000</v>
       </c>
       <c r="V72" s="3">
+        <v>9126000</v>
+      </c>
+      <c r="W72" s="3">
         <v>9794500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7499600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7420300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6436900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6776800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6156600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6344400</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5497,8 +5674,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5577,8 +5757,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5657,88 +5840,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22344000</v>
+      </c>
+      <c r="E76" s="3">
         <v>21118000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21606000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21874000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20725000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20014000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20853000</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L76" s="3">
         <v>20694000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22156000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20232000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19376000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19655000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18283000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19027000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17790000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18349000</v>
-      </c>
-      <c r="T76" s="3">
-        <v>15476000</v>
       </c>
       <c r="U76" s="3">
         <v>15476000</v>
       </c>
       <c r="V76" s="3">
+        <v>15476000</v>
+      </c>
+      <c r="W76" s="3">
         <v>17332900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14851800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15255600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14109000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14601600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14697300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11944700</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5817,173 +6006,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42916</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42735</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42551</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42369</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42185</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1319000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-94000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>703000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1376000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1297000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>116000</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>1306000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1199000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>884000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2722000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>785000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>719000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>403000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1123000</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T81" s="3">
         <v>593000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2885000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1461000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2485700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>402100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1364800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>313000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>760700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>54000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6012,88 +6210,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>424000</v>
+      </c>
+      <c r="E83" s="3">
         <v>397000</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>402000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>401000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>384000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>339500</v>
       </c>
       <c r="J83" s="3">
         <v>339500</v>
       </c>
       <c r="K83" s="3">
+        <v>339500</v>
+      </c>
+      <c r="L83" s="3">
         <v>397500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>309500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1765000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>848000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>868000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>826000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T83" s="3">
         <v>-445000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>265000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>518000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>650700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>584800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1185800</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>596900</v>
       </c>
       <c r="Z83" s="3">
         <v>596900</v>
       </c>
       <c r="AA83" s="3">
+        <v>596900</v>
+      </c>
+      <c r="AB83" s="3">
         <v>429600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6172,8 +6374,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6252,8 +6457,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6332,8 +6540,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6412,8 +6623,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6492,88 +6706,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1378000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-659000</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>1486000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1485000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-712000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>1631000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1634000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1589500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4210000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1565000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2930000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1008000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T89" s="3">
         <v>-1940000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>57000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-311000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2677100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-54300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2569300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>77400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2822900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-315800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1747800</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6602,88 +6822,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-655000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-645000</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-505000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-624000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-506000</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-404000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-439000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-463500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-967000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-587000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-482000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-514000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-656000</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T91" s="3">
         <v>486000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-77000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-509000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-635200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-568200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-936600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-457800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-610400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-396700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-260600</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6762,8 +6986,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6842,88 +7069,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-831000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-964000</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1788000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-521000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2096000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>-759000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-478000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1521000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2546000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-519000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-613000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-447000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T94" s="3">
         <v>1026000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1093000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1321000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2039500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1085400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-807000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-445400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8485600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>301700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6952,88 +7185,92 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3">
+        <v>500000</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>238000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>481000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>750000</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>761000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>92500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-906000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-729000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-170000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-537000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>96000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-52000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-358000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-116000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-412000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-386500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-260300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-161600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-275800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-135000</v>
       </c>
     </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7112,8 +7349,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7192,8 +7432,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7272,244 +7515,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1153000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1141000</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>-629000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-339000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-176000</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
         <v>649000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1555000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-514500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3305000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2368000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4992000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5279000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T100" s="3">
         <v>-544000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-456000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1337000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-311000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>667900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1901700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-859400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2637800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2125800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>610400</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-97000</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3">
         <v>-74000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>24000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>68000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>1000</v>
       </c>
       <c r="J101" s="3">
         <v>1000</v>
       </c>
       <c r="K101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L101" s="3">
         <v>-116500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-95000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-297000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-107000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>308000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>30000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T101" s="3">
         <v>-11000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>178000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-81300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-103000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>63700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-33700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>170200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>132600</v>
       </c>
     </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-476000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-407000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-866000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>637000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3081000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>1447000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-375000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-445000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1938000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1429000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2367000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5870000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T102" s="3">
         <v>-1158000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>525000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-287000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>245200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-574800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-75800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1261100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3052900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2281900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2522500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>CRH</t>
   </si>
@@ -656,393 +656,405 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9416000</v>
+      </c>
+      <c r="E8" s="3">
         <v>11069000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10206000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6756000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8870000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10515000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9654000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6533000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>10128000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9709000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8862500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29206000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13167000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15372000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12215000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15285000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8583000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12847000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>27449000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11944000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11726300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13125100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>27218300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14241400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16005200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10998600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12428300</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6060000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6760000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6180000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4919000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5710000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6456000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5979000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4726000</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>6365000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6079000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5832500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19379000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8867000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10060000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8365000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10130000</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V9" s="3">
         <v>8729000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18391000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8236000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7398500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8960500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>18189500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9780400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>10894500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7845700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8641600</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3356000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4309000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4026000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1837000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3160000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4059000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3675000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1807000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>3763000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3630000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3030000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9827000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4300000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5312000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3850000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5155000</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V10" s="3">
         <v>4118000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9058000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3708000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4327900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4164600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9028900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4461000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5110700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3152900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3786700</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1073,8 +1085,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1159,8 +1172,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1245,80 +1261,83 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-98000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-3000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>17000</v>
       </c>
-      <c r="G14" s="3">
-        <v>115000</v>
-      </c>
       <c r="H14" s="3">
+        <v>136000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-120000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-121000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-148000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>-11000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-18000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>45500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>25000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>5000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>5000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>2000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>21000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>12000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>5500</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1331,52 +1350,55 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>550000</v>
+      </c>
+      <c r="E15" s="3">
         <v>601000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>528000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>477000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>510000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>467000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>424000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>397000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>446000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>402000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>401000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>376000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>46000</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1417,8 +1439,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1446,180 +1471,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7998000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9077000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8285000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6743000</v>
       </c>
-      <c r="G17" s="3">
-        <v>7639000</v>
-      </c>
       <c r="H17" s="3">
+        <v>7618000</v>
+      </c>
+      <c r="I17" s="3">
         <v>8611000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7922000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6492000</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>8350000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8112000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7641000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25879000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12142000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13873000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11451000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13288000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V17" s="3">
         <v>12051000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25003000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11352000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10147400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12452700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>25123300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13581700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>14784500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10776700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>11552600</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1418000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1992000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1921000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1231000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1252000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1904000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1732000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>41000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>1778000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1597000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1221500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3327000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1025000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1499000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>764000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1997000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V18" s="3">
         <v>796000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2446000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>592000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1579000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>672300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2095000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>659700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1220700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>221900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>875700</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1650,224 +1682,231 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-26000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>135000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-25000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>-14000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-13000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-222000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-96000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-353000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-246000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-533000</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V20" s="3">
         <v>-79000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-478000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-95000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-131600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-146200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-316200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-203100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-132400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-147900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1977000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2619000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2450000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>480000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1606000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1627000</v>
+      </c>
+      <c r="I21" s="3">
         <v>2396000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2162000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>434000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>446000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2194000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2011000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1603500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4870000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1777000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2014000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1344000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3">
         <v>272000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2233000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1015000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2098100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1110900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2964600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1053500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1685200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>503600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1221900</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E22" s="3">
         <v>209000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>181000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>160000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>164000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>156000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>133000</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>131000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>73000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>82000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3000</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1908,180 +1947,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1283000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1947000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1757000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-156000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>852000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1920000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1739000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>95000</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>1734000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1591000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1129000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3102000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>929000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1146000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>518000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1464000</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V23" s="3">
         <v>717000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1968000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>497000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1447400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>526100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1778800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>456600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1088300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>74000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>821700</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E24" s="3">
         <v>428000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>425000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-58000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>143000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>531000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>430000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-19000</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>416000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>379000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>248500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>650000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>201000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>387000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>112000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>375000</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V24" s="3">
         <v>159000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>467000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>119000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-140000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>142900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>473200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>127900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>323100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>18800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2166,180 +2214,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1037000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1519000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1332000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-98000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>709000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1389000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1309000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>114000</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>1318000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1212000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>880500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2452000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>728000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>759000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>406000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1089000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V26" s="3">
         <v>558000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1501000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>378000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1587400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>383200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1305500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>328700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>765200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>55200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>631500</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1022000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1496000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1313000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-101000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>699000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1353000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1294000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>112000</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>1300000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1197000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>904000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2451000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>698000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>719000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>403000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1076000</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V27" s="3">
         <v>551000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1497000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>378000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1570600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>373300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1275900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>313000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>760700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>54000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2424,8 +2481,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2460,47 +2520,47 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>11000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>271000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>87000</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>47000</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3">
         <v>42000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>1388000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>1083000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>915100</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>28800</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>88900</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2510,8 +2570,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2596,8 +2659,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2682,180 +2748,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E32" s="3">
         <v>26000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-135000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>25000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>14000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>13000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>222000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>96000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>353000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>246000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>533000</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V32" s="3">
         <v>79000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>478000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>95000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>131600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>146200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>316200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>203100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>132400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>147900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>54000</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1025000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1503000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1319000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-94000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>703000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1376000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1297000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>116000</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>1306000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1199000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>884000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2722000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>785000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>719000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>403000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1123000</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V33" s="3">
         <v>593000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2885000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1461000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2485700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>402100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1364800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>313000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>760700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>54000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2940,185 +3015,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1025000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1503000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1319000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-94000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>703000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1376000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1297000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>116000</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>1306000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1199000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>884000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2722000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>785000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>719000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>403000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1123000</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V35" s="3">
         <v>593000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2885000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1461000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2485700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>402100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1364800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>313000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>760700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>54000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3149,8 +3233,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3181,94 +3266,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4096000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4198000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2876000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3352000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3720000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2978000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3066000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3308000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6341000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N41" s="3">
         <v>4275000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5936000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5783000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6292000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7721000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>14661000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9918000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1592000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9191000</v>
-      </c>
-      <c r="V41" s="3">
-        <v>1848000</v>
       </c>
       <c r="W41" s="3">
         <v>1848000</v>
       </c>
       <c r="X41" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="Y41" s="3">
         <v>2530000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2137700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2689000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1564100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2825200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6149600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3829000</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3353,610 +3442,634 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5452000</v>
+      </c>
+      <c r="E43" s="3">
         <v>7108000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6704000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5493000</v>
       </c>
-      <c r="G43" s="3">
-        <v>4820000</v>
-      </c>
       <c r="H43" s="3">
+        <v>5036000</v>
+      </c>
+      <c r="I43" s="3">
         <v>6422000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5893000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4798000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4507000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3">
         <v>6450000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4300000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4611000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5335000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4122000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4946000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4253000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6008000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4682000</v>
-      </c>
-      <c r="V43" s="3">
-        <v>5091000</v>
       </c>
       <c r="W43" s="3">
         <v>5091000</v>
       </c>
       <c r="X43" s="3">
+        <v>5091000</v>
+      </c>
+      <c r="Y43" s="3">
         <v>4539600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5396200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4373300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5548200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4467800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4211600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3121200</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5251000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5019000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5051000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4960000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4755000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4644000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4514000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4619000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4291000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3">
         <v>4276000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4194000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3611000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3193000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3117000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2940000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3080000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3673000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3505000</v>
-      </c>
-      <c r="V44" s="3">
-        <v>3151000</v>
       </c>
       <c r="W44" s="3">
         <v>3151000</v>
       </c>
       <c r="X44" s="3">
+        <v>3151000</v>
+      </c>
+      <c r="Y44" s="3">
         <v>3247700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3450200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3227000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3362600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3223500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2978000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2652800</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E45" s="3">
         <v>41000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>69000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>46000</v>
       </c>
-      <c r="G45" s="3">
-        <v>446000</v>
-      </c>
       <c r="H45" s="3">
+        <v>230000</v>
+      </c>
+      <c r="I45" s="3">
         <v>371000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>428000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>626000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1461000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>8000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>134000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17000</v>
-      </c>
-      <c r="V45" s="3">
-        <v>31000</v>
       </c>
       <c r="W45" s="3">
         <v>31000</v>
       </c>
       <c r="X45" s="3">
+        <v>31000</v>
+      </c>
+      <c r="Y45" s="3">
         <v>1370800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>66500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>25300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>29200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>26900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>25800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>640900</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15254000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16852000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15151000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14242000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14083000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14840000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15113000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13709000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16885000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N46" s="3">
         <v>15009000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14833000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14044000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14855000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14977000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>22574000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17258000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11283000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17395000</v>
-      </c>
-      <c r="V46" s="3">
-        <v>10121000</v>
       </c>
       <c r="W46" s="3">
         <v>10121000</v>
       </c>
       <c r="X46" s="3">
+        <v>10121000</v>
+      </c>
+      <c r="Y46" s="3">
         <v>11688100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11050500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10314600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10504100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10543300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13365000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10243800</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>502000</v>
+      </c>
+      <c r="E47" s="3">
         <v>743000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>712000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>732000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>737000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>929000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>484000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>609000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>620000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>714000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>649000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>904000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>875000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>964000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1049000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1144000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1575000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1565000</v>
-      </c>
-      <c r="V47" s="3">
-        <v>1299000</v>
       </c>
       <c r="W47" s="3">
         <v>1299000</v>
       </c>
       <c r="X47" s="3">
+        <v>1299000</v>
+      </c>
+      <c r="Y47" s="3">
         <v>1709400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1641500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1687600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1688600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1676300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1814700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1686800</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26408000</v>
+      </c>
+      <c r="E48" s="3">
         <v>25195000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24312000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23451000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22726000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22611000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20514000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20163000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19133000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>19322000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18943000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19502000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19100000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19317000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19099000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>39148000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>38153000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18046000</v>
-      </c>
-      <c r="V48" s="3">
-        <v>15607000</v>
       </c>
       <c r="W48" s="3">
         <v>15607000</v>
       </c>
       <c r="X48" s="3">
+        <v>15607000</v>
+      </c>
+      <c r="Y48" s="3">
         <v>15663000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13744200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13933600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>14146000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>14655400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9181500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8712000</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15147000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14822000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12912000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12683000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12272000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12011000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11337000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11218000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10199000</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>10399000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10287000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9848000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9468000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9373000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9378000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9475000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9702000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9656000</v>
-      </c>
-      <c r="V49" s="3">
-        <v>8615000</v>
       </c>
       <c r="W49" s="3">
         <v>8615000</v>
       </c>
       <c r="X49" s="3">
+        <v>8615000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>8629400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8360200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8521600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8629200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8774000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5177700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4898300</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4041,8 +4154,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4127,94 +4243,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1018000</v>
+      </c>
+      <c r="E52" s="3">
         <v>915000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>897000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>813000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>795000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>830000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>657000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>634000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>632000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3">
         <v>456000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>607000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>372000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>231000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>313000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>275000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>161000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>166000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>115000</v>
-      </c>
-      <c r="V52" s="3">
-        <v>114000</v>
       </c>
       <c r="W52" s="3">
         <v>114000</v>
       </c>
       <c r="X52" s="3">
+        <v>114000</v>
+      </c>
+      <c r="Y52" s="3">
         <v>149500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>200500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>232800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>362400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>262500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>253500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>302800</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4299,94 +4421,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58329000</v>
+      </c>
+      <c r="E54" s="3">
         <v>58527000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>53984000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>51921000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>50613000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>51221000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>48105000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>46333000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>47469000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N54" s="3">
         <v>45983000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>45319000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>44670000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>44529000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44944000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>52375000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47612000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>43034000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>46777000</v>
-      </c>
-      <c r="V54" s="3">
-        <v>35756000</v>
       </c>
       <c r="W54" s="3">
         <v>35756000</v>
       </c>
       <c r="X54" s="3">
+        <v>35756000</v>
+      </c>
+      <c r="Y54" s="3">
         <v>37839400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34996800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34690200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>35330300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>35911500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>29792500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>25843800</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4417,8 +4545,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4449,524 +4578,543 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3263000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3156000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3303000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2777000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3207000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2963000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3363000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2730000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3149000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3">
         <v>7448000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2930000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5692000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6198000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4792000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5031000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4916000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5773000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5277000</v>
-      </c>
-      <c r="V57" s="3">
-        <v>5155000</v>
       </c>
       <c r="W57" s="3">
         <v>5155000</v>
       </c>
       <c r="X57" s="3">
+        <v>5155000</v>
+      </c>
+      <c r="Y57" s="3">
         <v>5423600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5538000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5286900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5880300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5341800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4145900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3397000</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1577000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4322000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1418000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1705000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3331000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3549000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3477000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3247000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2152000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>2490000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1751000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>846000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>452000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1553000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6185000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6920000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1571000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7213000</v>
-      </c>
-      <c r="V58" s="3">
-        <v>1356000</v>
       </c>
       <c r="W58" s="3">
         <v>1356000</v>
       </c>
       <c r="X58" s="3">
+        <v>1356000</v>
+      </c>
+      <c r="Y58" s="3">
         <v>378000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>463000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>302000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>720300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>848200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>412000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>524700</v>
       </c>
     </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1341000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1560000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1513000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1770000</v>
       </c>
-      <c r="G59" s="3">
-        <v>1325000</v>
-      </c>
       <c r="H59" s="3">
+        <v>1222000</v>
+      </c>
+      <c r="I59" s="3">
         <v>1465000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1274000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1620000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2245000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>1289000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1034000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1043000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1262000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1120000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1125000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1030000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1005000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>976000</v>
-      </c>
-      <c r="V59" s="3">
-        <v>984000</v>
       </c>
       <c r="W59" s="3">
         <v>984000</v>
       </c>
       <c r="X59" s="3">
+        <v>984000</v>
+      </c>
+      <c r="Y59" s="3">
         <v>1412700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>898300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>887200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>880800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>955900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>322800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>617400</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8754000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11596000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8684000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8712000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10296000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10668000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10548000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9997000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10013000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N60" s="3">
         <v>11227000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8041000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7581000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7912000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7465000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12341000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12866000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8349000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13466000</v>
-      </c>
-      <c r="V60" s="3">
-        <v>7495000</v>
       </c>
       <c r="W60" s="3">
         <v>7495000</v>
       </c>
       <c r="X60" s="3">
+        <v>7495000</v>
+      </c>
+      <c r="Y60" s="3">
         <v>7214300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6899200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6476000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7481400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7146000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4880700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4539100</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18128000</v>
+      </c>
+      <c r="E61" s="3">
         <v>16331000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16180000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15624000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12233000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11957000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11161000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10945000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10987000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>8727000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9204000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11312000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11995000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10958000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>15108000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10604000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11731000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9959000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>8557000</v>
       </c>
       <c r="W61" s="3">
         <v>8557000</v>
       </c>
       <c r="X61" s="3">
+        <v>8557000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>9162900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8838600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8251500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8908600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9497600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7241200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6360900</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2210000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2137000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2050000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1858000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1906000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2005000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1781000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1715000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1856000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>1470000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1877000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4863000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4550000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6173000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6000000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4507000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4543000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4400000</v>
-      </c>
-      <c r="V62" s="3">
-        <v>3733000</v>
       </c>
       <c r="W62" s="3">
         <v>3733000</v>
       </c>
       <c r="X62" s="3">
+        <v>3733000</v>
+      </c>
+      <c r="Y62" s="3">
         <v>3546700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3845600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4104300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4229900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4071700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2946300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2973300</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5051,8 +5199,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5137,8 +5288,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5223,94 +5377,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32851000</v>
+      </c>
+      <c r="E66" s="3">
         <v>33898000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>30354000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>29564000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27763000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>28055000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26654000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25591000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25848000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N66" s="3">
         <v>24637000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22279000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24437000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25152000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25288000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>34091000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28584000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25243000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28427000</v>
-      </c>
-      <c r="V66" s="3">
-        <v>20279000</v>
       </c>
       <c r="W66" s="3">
         <v>20279000</v>
       </c>
       <c r="X66" s="3">
+        <v>20279000</v>
+      </c>
+      <c r="Y66" s="3">
         <v>20505300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20143900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19433500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>21220200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21308800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15094000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13897900</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5341,8 +5501,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5427,8 +5588,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5513,8 +5677,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5543,10 +5710,10 @@
         <v>1000</v>
       </c>
       <c r="L70" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M70" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>1000</v>
@@ -5579,10 +5746,10 @@
         <v>1000</v>
       </c>
       <c r="X70" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y70" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>1100</v>
       </c>
       <c r="Z70" s="3">
         <v>1100</v>
@@ -5594,13 +5761,16 @@
         <v>1100</v>
       </c>
       <c r="AC70" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AD70" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5685,94 +5855,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>25593000</v>
+      </c>
+      <c r="E72" s="3">
         <v>25068000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>24106000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>23375000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>24036000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>23831000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23030000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22346000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22918000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3">
         <v>21712000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>22495000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20215000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19463000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12009000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>11501000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11761000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11929000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12083000</v>
-      </c>
-      <c r="V72" s="3">
-        <v>9126000</v>
       </c>
       <c r="W72" s="3">
         <v>9126000</v>
       </c>
       <c r="X72" s="3">
+        <v>9126000</v>
+      </c>
+      <c r="Y72" s="3">
         <v>9794500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7499600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7420300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6436900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6776800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6156600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6344400</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5857,8 +6033,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5943,8 +6122,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6029,94 +6211,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24003000</v>
+      </c>
+      <c r="E76" s="3">
         <v>23308000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22344000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21118000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21606000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21874000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20725000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20014000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20853000</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N76" s="3">
         <v>20694000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22156000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20232000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19376000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19655000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18283000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19027000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17790000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18349000</v>
-      </c>
-      <c r="V76" s="3">
-        <v>15476000</v>
       </c>
       <c r="W76" s="3">
         <v>15476000</v>
       </c>
       <c r="X76" s="3">
+        <v>15476000</v>
+      </c>
+      <c r="Y76" s="3">
         <v>17332900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14851800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15255600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14109000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14601600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14697300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11944700</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6201,185 +6389,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1025000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1503000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1319000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-94000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>703000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1376000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1297000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>116000</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>1306000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1199000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>884000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2722000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>785000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>719000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>403000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1123000</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V81" s="3">
         <v>593000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2885000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1461000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2485700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>402100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1364800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>313000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>760700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>54000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6410,94 +6607,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>358000</v>
+      </c>
+      <c r="E83" s="3">
         <v>467000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>424000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>397000</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
         <v>402000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>401000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>384000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>339500</v>
       </c>
       <c r="L83" s="3">
         <v>339500</v>
       </c>
       <c r="M83" s="3">
+        <v>339500</v>
+      </c>
+      <c r="N83" s="3">
         <v>397500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>309500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1765000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>848000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>868000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>826000</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V83" s="3">
         <v>-445000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>265000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>518000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>650700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>584800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1185800</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>596900</v>
       </c>
       <c r="AB83" s="3">
         <v>596900</v>
       </c>
       <c r="AC83" s="3">
+        <v>596900</v>
+      </c>
+      <c r="AD83" s="3">
         <v>429600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6582,8 +6783,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6668,8 +6872,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6754,8 +6961,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6840,8 +7050,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6926,94 +7139,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2915000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1991000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1378000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-659000</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H89" s="3">
+        <v>2730000</v>
+      </c>
+      <c r="I89" s="3">
         <v>1486000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1485000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-712000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M89" s="3">
         <v>1631000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1634000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1589500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4210000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1565000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2930000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1008000</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V89" s="3">
         <v>-1940000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>57000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-311000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2677100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-54300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2569300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>77400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2822900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-315800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1747800</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7044,94 +7263,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-821000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-592000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-655000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-645000</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H91" s="3">
+        <v>-943000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-505000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-624000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-506000</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
         <v>-404000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-439000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-463500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-967000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-587000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-482000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-514000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-656000</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V91" s="3">
         <v>486000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-77000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-509000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-635200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-568200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-936600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-457800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-610400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-396700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-260600</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7216,8 +7439,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7302,94 +7528,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1340000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2910000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-831000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-964000</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1886000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1788000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-521000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2096000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M94" s="3">
         <v>-759000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-478000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1521000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2546000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-519000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-613000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-447000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V94" s="3">
         <v>1026000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1093000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1321000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2039500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1085400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-807000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-445400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8485600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>301700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7420,94 +7652,98 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E96" s="3">
         <v>249000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>500000</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H96" s="3">
+        <v>237000</v>
+      </c>
+      <c r="I96" s="3">
         <v>238000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>481000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>750000</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>761000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>92500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-906000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-729000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-170000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-537000</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>96000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-52000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-358000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-116000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-412000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-386500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-260300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-161600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-275800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-135000</v>
       </c>
     </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7592,8 +7828,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7678,8 +7917,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7764,262 +8006,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1723000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2331000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1153000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1141000</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H100" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-629000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-339000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-176000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M100" s="3">
         <v>649000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1555000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-514500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3305000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2368000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4992000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5279000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V100" s="3">
         <v>-544000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-456000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1337000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-311000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>667900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1901700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-859400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2637800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2125800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>610400</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="E101" s="3">
         <v>65000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>12000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-97000</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
         <v>-74000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>24000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>68000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>1000</v>
       </c>
       <c r="L101" s="3">
         <v>1000</v>
       </c>
       <c r="M101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N101" s="3">
         <v>-116500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-95000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-297000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-107000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>308000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>30000</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V101" s="3">
         <v>-11000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>178000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-81300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-103000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>63700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-33700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>170200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>132600</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-141000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1412000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-476000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-407000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>679000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-866000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>637000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3081000</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>1447000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-375000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-445000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1938000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1429000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2367000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5870000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V102" s="3">
         <v>-1158000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>525000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-287000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>245200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-574800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-75800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1261100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3052900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2281900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2522500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>CRH</t>
   </si>
@@ -656,405 +656,418 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42916</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42735</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42551</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42369</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42185</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7370000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9416000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11069000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10206000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6756000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8870000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10515000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9654000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6533000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>10128000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9709000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8862500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29206000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13167000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15372000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12215000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15285000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8583000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12847000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>27449000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11944000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11726300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>13125100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>27218300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14241400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16005200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10998600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12428300</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5325000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6060000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6760000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6180000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4919000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5710000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6456000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5979000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4726000</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>6365000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6079000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5832500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19379000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8867000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10060000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8365000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10130000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W9" s="3">
         <v>8729000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>18391000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8236000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7398500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8960500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>18189500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9780400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>10894500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7845700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8641600</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2045000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3356000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4309000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4026000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1837000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3160000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4059000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3675000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1807000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>3763000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3630000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3030000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9827000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4300000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5312000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3850000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5155000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W10" s="3">
         <v>4118000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9058000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3708000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4327900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4164600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9028900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4461000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5110700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3152900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3786700</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,8 +1099,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,8 +1189,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,83 +1281,86 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-34000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-98000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>17000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>136000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-120000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-121000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-148000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>-11000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-18000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>45500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>25000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>5000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>2000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>21000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>5500</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1353,55 +1373,58 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>576000</v>
+      </c>
+      <c r="E15" s="3">
         <v>550000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>601000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>528000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>477000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>510000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>467000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>424000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>397000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>446000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>402000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>401000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>376000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>46000</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1442,8 +1465,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1498,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7373000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7998000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9077000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8285000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6743000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7618000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8611000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7922000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6492000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>8350000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8112000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7641000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25879000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12142000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13873000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11451000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13288000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W17" s="3">
         <v>12051000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>25003000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>11352000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10147400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12452700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>25123300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13581700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>14784500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10776700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>11552600</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1418000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1992000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1921000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1252000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1904000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1732000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>41000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>1778000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1597000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1221500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3327000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1025000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1499000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>764000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1997000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W18" s="3">
         <v>796000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2446000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>592000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1579000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>672300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2095000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>659700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1220700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>221900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>875700</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,233 +1716,240 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-9000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-26000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>10000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>135000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-25000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>-14000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-222000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-96000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-353000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-246000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-533000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W20" s="3">
         <v>-79000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-478000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-95000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-131600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-146200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-316200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-203100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-132400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-147900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-54000</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>562000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1977000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2619000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2450000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>480000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1627000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2396000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2162000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>434000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>446000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2194000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2011000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1603500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4870000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1777000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2014000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1344000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W21" s="3">
         <v>272000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2233000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1015000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2098100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1110900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2964600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1053500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1685200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>503600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1221900</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E22" s="3">
         <v>220000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>209000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>181000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>160000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>164000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>156000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>133000</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>131000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>73000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>82000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3000</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1950,186 +1990,195 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-235000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1283000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1947000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1757000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-156000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>852000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1920000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1739000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>95000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>1734000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1591000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1129000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3102000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>929000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1146000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>518000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1464000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W23" s="3">
         <v>717000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1968000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>497000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1447400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>526100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1778800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>456600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1088300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>74000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>821700</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E24" s="3">
         <v>246000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>428000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>425000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-58000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>143000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>531000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>430000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-19000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>416000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>379000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>248500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>650000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>201000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>387000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>112000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>375000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W24" s="3">
         <v>159000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>467000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>119000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-140000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>142900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>473200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>127900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>323100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>18800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>190200</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2266,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-180000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1037000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1519000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1332000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-98000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>709000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1389000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1309000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>114000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>1318000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1212000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>880500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2452000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>728000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>759000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>406000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1089000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W26" s="3">
         <v>558000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1501000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>378000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1587400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>383200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1305500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>328700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>765200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>55200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>631500</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1022000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1496000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1313000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-101000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>699000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1353000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1294000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>112000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>1300000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1197000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>904000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2451000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>698000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>719000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>403000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1076000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W27" s="3">
         <v>551000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1497000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>378000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1570600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>373300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1275900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>313000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>760700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>54000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2542,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2523,47 +2584,47 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>11000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>271000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>87000</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>47000</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>42000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>1388000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>1083000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>915100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>28800</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>88900</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2573,8 +2634,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2726,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,186 +2818,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E32" s="3">
         <v>9000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>26000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-10000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-135000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>25000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>14000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>222000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>96000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>353000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>246000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>533000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W32" s="3">
         <v>79000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>478000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>95000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>131600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>146200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>316200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>203100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>132400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>147900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>54000</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-176000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1025000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1503000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1319000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-94000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>703000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1376000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1297000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>116000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>1306000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1199000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>884000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2722000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>785000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>719000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>403000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1123000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W33" s="3">
         <v>593000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2885000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1461000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2485700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>402100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1364800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>313000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>760700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>54000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3094,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-176000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1025000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1503000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1319000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-94000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>703000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1376000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1297000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>116000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>1306000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1199000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>884000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2722000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>785000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>719000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>403000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1123000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W35" s="3">
         <v>593000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2885000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1461000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2485700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>402100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1364800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>313000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>760700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>54000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42916</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42735</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42551</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42369</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42185</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3319,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,97 +3353,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3240000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4096000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4198000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2876000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3352000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3720000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2978000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3066000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3308000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6341000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O41" s="3">
         <v>4275000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5936000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5783000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6292000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7721000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14661000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9918000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1592000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9191000</v>
-      </c>
-      <c r="W41" s="3">
-        <v>1848000</v>
       </c>
       <c r="X41" s="3">
         <v>1848000</v>
       </c>
       <c r="Y41" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="Z41" s="3">
         <v>2530000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2137700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2689000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1564100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2825200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6149600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3829000</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3445,631 +3535,655 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5506000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5452000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7108000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6704000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5493000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5036000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6422000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5893000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4798000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4507000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O43" s="3">
         <v>6450000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4300000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4611000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5335000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4122000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4946000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4253000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6008000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4682000</v>
-      </c>
-      <c r="W43" s="3">
-        <v>5091000</v>
       </c>
       <c r="X43" s="3">
         <v>5091000</v>
       </c>
       <c r="Y43" s="3">
+        <v>5091000</v>
+      </c>
+      <c r="Z43" s="3">
         <v>4539600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5396200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4373300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5548200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4467800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4211600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3121200</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5058000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5251000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5019000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5051000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4960000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4755000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4644000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4514000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4619000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4291000</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3">
         <v>4276000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4194000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3611000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3193000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3117000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2940000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3080000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3673000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3505000</v>
-      </c>
-      <c r="W44" s="3">
-        <v>3151000</v>
       </c>
       <c r="X44" s="3">
         <v>3151000</v>
       </c>
       <c r="Y44" s="3">
+        <v>3151000</v>
+      </c>
+      <c r="Z44" s="3">
         <v>3247700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3450200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3227000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3362600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3223500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2978000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2652800</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1900000</v>
+      </c>
+      <c r="E45" s="3">
         <v>10000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>41000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>69000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>46000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>230000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>371000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>428000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>626000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1461000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>8000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>134000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>35000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>27000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17000</v>
-      </c>
-      <c r="W45" s="3">
-        <v>31000</v>
       </c>
       <c r="X45" s="3">
         <v>31000</v>
       </c>
       <c r="Y45" s="3">
+        <v>31000</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1370800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>66500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>25300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>29200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>26900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>25800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>640900</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16239000</v>
+      </c>
+      <c r="E46" s="3">
         <v>15254000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16852000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15151000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14242000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14083000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14840000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15113000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13709000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16885000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O46" s="3">
         <v>15009000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14833000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14044000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14855000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14977000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>22574000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17258000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11283000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17395000</v>
-      </c>
-      <c r="W46" s="3">
-        <v>10121000</v>
       </c>
       <c r="X46" s="3">
         <v>10121000</v>
       </c>
       <c r="Y46" s="3">
+        <v>10121000</v>
+      </c>
+      <c r="Z46" s="3">
         <v>11688100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11050500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10314600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10504100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10543300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>13365000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10243800</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>487000</v>
+      </c>
+      <c r="E47" s="3">
         <v>502000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>743000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>712000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>732000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>737000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>929000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>484000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>609000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>620000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
         <v>714000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>649000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>904000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>875000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>964000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1049000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1144000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1575000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1565000</v>
-      </c>
-      <c r="W47" s="3">
-        <v>1299000</v>
       </c>
       <c r="X47" s="3">
         <v>1299000</v>
       </c>
       <c r="Y47" s="3">
+        <v>1299000</v>
+      </c>
+      <c r="Z47" s="3">
         <v>1709400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1641500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1687600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1688600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1676300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1814700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1686800</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25931000</v>
+      </c>
+      <c r="E48" s="3">
         <v>26408000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>25195000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24312000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23451000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22726000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22611000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20514000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20163000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19133000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O48" s="3">
         <v>19322000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18943000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19502000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19100000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19317000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19099000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>39148000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>38153000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18046000</v>
-      </c>
-      <c r="W48" s="3">
-        <v>15607000</v>
       </c>
       <c r="X48" s="3">
         <v>15607000</v>
       </c>
       <c r="Y48" s="3">
+        <v>15607000</v>
+      </c>
+      <c r="Z48" s="3">
         <v>15663000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13744200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13933600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>14146000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>14655400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9181500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8712000</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14548000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15147000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14822000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12912000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12683000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12272000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12011000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11337000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11218000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10199000</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>10399000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10287000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9848000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9468000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9373000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9378000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9475000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9702000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9656000</v>
-      </c>
-      <c r="W49" s="3">
-        <v>8615000</v>
       </c>
       <c r="X49" s="3">
         <v>8615000</v>
       </c>
       <c r="Y49" s="3">
+        <v>8615000</v>
+      </c>
+      <c r="Z49" s="3">
         <v>8629400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8360200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8521600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8629200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8774000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5177700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4898300</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4271,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,97 +4363,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>962000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1018000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>915000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>897000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>813000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>795000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>830000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>657000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>634000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>632000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O52" s="3">
         <v>456000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>607000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>372000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>231000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>313000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>275000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>161000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>166000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>115000</v>
-      </c>
-      <c r="W52" s="3">
-        <v>114000</v>
       </c>
       <c r="X52" s="3">
         <v>114000</v>
       </c>
       <c r="Y52" s="3">
+        <v>114000</v>
+      </c>
+      <c r="Z52" s="3">
         <v>149500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>200500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>232800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>362400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>262500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>253500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>302800</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4547,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58167000</v>
+      </c>
+      <c r="E54" s="3">
         <v>58329000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>58527000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>53984000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>51921000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>50613000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51221000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>48105000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>46333000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47469000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O54" s="3">
         <v>45983000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>45319000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>44670000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44529000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>44944000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>52375000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>47612000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>43034000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>46777000</v>
-      </c>
-      <c r="W54" s="3">
-        <v>35756000</v>
       </c>
       <c r="X54" s="3">
         <v>35756000</v>
       </c>
       <c r="Y54" s="3">
+        <v>35756000</v>
+      </c>
+      <c r="Z54" s="3">
         <v>37839400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34996800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>34690200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>35330300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>35911500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29792500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>25843800</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4675,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,542 +4709,561 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2947000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3263000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3156000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3303000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2777000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3207000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2963000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3363000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2730000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3149000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O57" s="3">
         <v>7448000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2930000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5692000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6198000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4792000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5031000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4916000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5773000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5277000</v>
-      </c>
-      <c r="W57" s="3">
-        <v>5155000</v>
       </c>
       <c r="X57" s="3">
         <v>5155000</v>
       </c>
       <c r="Y57" s="3">
+        <v>5155000</v>
+      </c>
+      <c r="Z57" s="3">
         <v>5423600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5538000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5286900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5880300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5341800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4145900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3397000</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2843000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1577000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4322000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1418000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1705000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3331000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3549000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3477000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3247000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2152000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>2490000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1751000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>846000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>452000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1553000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6185000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6920000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1571000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7213000</v>
-      </c>
-      <c r="W58" s="3">
-        <v>1356000</v>
       </c>
       <c r="X58" s="3">
         <v>1356000</v>
       </c>
       <c r="Y58" s="3">
+        <v>1356000</v>
+      </c>
+      <c r="Z58" s="3">
         <v>378000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>463000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>302000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>720300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>848200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>412000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>524700</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1854000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1341000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1560000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1513000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1770000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1222000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1465000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1274000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1620000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2245000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O59" s="3">
         <v>1289000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1034000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1043000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1262000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1120000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1125000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1030000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1005000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>976000</v>
-      </c>
-      <c r="W59" s="3">
-        <v>984000</v>
       </c>
       <c r="X59" s="3">
         <v>984000</v>
       </c>
       <c r="Y59" s="3">
+        <v>984000</v>
+      </c>
+      <c r="Z59" s="3">
         <v>1412700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>898300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>887200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>880800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>955900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>322800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>617400</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10211000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8754000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11596000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8684000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8712000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10296000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10668000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10548000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9997000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10013000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O60" s="3">
         <v>11227000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8041000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7581000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7912000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7465000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12341000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12866000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8349000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13466000</v>
-      </c>
-      <c r="W60" s="3">
-        <v>7495000</v>
       </c>
       <c r="X60" s="3">
         <v>7495000</v>
       </c>
       <c r="Y60" s="3">
+        <v>7495000</v>
+      </c>
+      <c r="Z60" s="3">
         <v>7214300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6899200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6476000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7481400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7146000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4880700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4539100</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17585000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18128000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16331000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16180000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15624000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12233000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11957000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11161000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10945000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10987000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>8727000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9204000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11312000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11995000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10958000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>15108000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10604000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11731000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9959000</v>
-      </c>
-      <c r="W61" s="3">
-        <v>8557000</v>
       </c>
       <c r="X61" s="3">
         <v>8557000</v>
       </c>
       <c r="Y61" s="3">
+        <v>8557000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>9162900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8838600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8251500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8908600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9497600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7241200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6360900</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2210000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2137000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2050000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1858000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1906000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2005000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1781000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1715000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1856000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O62" s="3">
         <v>1470000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1877000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4863000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4550000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6173000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6000000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4507000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4543000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4400000</v>
-      </c>
-      <c r="W62" s="3">
-        <v>3733000</v>
       </c>
       <c r="X62" s="3">
         <v>3733000</v>
       </c>
       <c r="Y62" s="3">
+        <v>3733000</v>
+      </c>
+      <c r="Z62" s="3">
         <v>3546700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3845600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4104300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4229900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4071700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2946300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2973300</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5351,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5443,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5535,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33622000</v>
+      </c>
+      <c r="E66" s="3">
         <v>32851000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33898000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30354000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>29564000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27763000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>28055000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26654000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25591000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25848000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O66" s="3">
         <v>24637000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22279000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24437000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>25152000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25288000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34091000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28584000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>25243000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>28427000</v>
-      </c>
-      <c r="W66" s="3">
-        <v>20279000</v>
       </c>
       <c r="X66" s="3">
         <v>20279000</v>
       </c>
       <c r="Y66" s="3">
+        <v>20279000</v>
+      </c>
+      <c r="Z66" s="3">
         <v>20505300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>20143900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19433500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21220200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21308800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15094000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13897900</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5663,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5753,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +5845,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5713,10 +5881,10 @@
         <v>1000</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N70" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>1000</v>
@@ -5749,10 +5917,10 @@
         <v>1000</v>
       </c>
       <c r="Y70" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z70" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>1100</v>
       </c>
       <c r="AA70" s="3">
         <v>1100</v>
@@ -5764,13 +5932,16 @@
         <v>1100</v>
       </c>
       <c r="AD70" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="AE70" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6029,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>24793000</v>
+      </c>
+      <c r="E72" s="3">
         <v>25593000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25068000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>24106000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>23375000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24036000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23831000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23030000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22346000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22918000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O72" s="3">
         <v>21712000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>22495000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20215000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19463000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12009000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11501000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11761000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11929000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12083000</v>
-      </c>
-      <c r="W72" s="3">
-        <v>9126000</v>
       </c>
       <c r="X72" s="3">
         <v>9126000</v>
       </c>
       <c r="Y72" s="3">
+        <v>9126000</v>
+      </c>
+      <c r="Z72" s="3">
         <v>9794500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7499600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7420300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6436900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6776800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6156600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6344400</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6213,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6305,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6397,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23070000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24003000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23308000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22344000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21118000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21606000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21874000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20725000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20014000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20853000</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O76" s="3">
         <v>20694000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22156000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20232000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19376000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19655000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18283000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19027000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17790000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18349000</v>
-      </c>
-      <c r="W76" s="3">
-        <v>15476000</v>
       </c>
       <c r="X76" s="3">
         <v>15476000</v>
       </c>
       <c r="Y76" s="3">
+        <v>15476000</v>
+      </c>
+      <c r="Z76" s="3">
         <v>17332900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14851800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15255600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14109000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14601600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14697300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11944700</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6581,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42916</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42735</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42551</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42369</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42185</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-176000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1025000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1503000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1319000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-94000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>703000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1376000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1297000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>116000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>1306000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1199000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>884000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2722000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>785000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>719000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>403000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1123000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W81" s="3">
         <v>593000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2885000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1461000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2485700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>402100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1364800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>313000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>760700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>54000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>630300</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,97 +6806,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E83" s="3">
         <v>358000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>467000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>424000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>397000</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>402000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>401000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>384000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>339500</v>
       </c>
       <c r="M83" s="3">
         <v>339500</v>
       </c>
       <c r="N83" s="3">
+        <v>339500</v>
+      </c>
+      <c r="O83" s="3">
         <v>397500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>309500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1765000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>848000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>868000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>826000</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W83" s="3">
         <v>-445000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>265000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>518000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>650700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>584800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1185800</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>596900</v>
       </c>
       <c r="AC83" s="3">
         <v>596900</v>
       </c>
       <c r="AD83" s="3">
+        <v>596900</v>
+      </c>
+      <c r="AE83" s="3">
         <v>429600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>400300</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +6988,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7080,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7172,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7264,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7356,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-616000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2915000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1991000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1378000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-659000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2730000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1486000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1485000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-712000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N89" s="3">
         <v>1631000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1634000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1589500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4210000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1565000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2930000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1008000</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W89" s="3">
         <v>-1940000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>57000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-311000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2677100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-54300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2569300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>77400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2822900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-315800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1747800</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,97 +7484,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-601000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-821000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-592000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-655000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-645000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-943000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-505000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-624000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-506000</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3">
         <v>-404000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-439000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-463500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-967000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-587000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-482000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-514000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-656000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W91" s="3">
         <v>486000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-77000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-509000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-635200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-568200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-936600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-457800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-610400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-396700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-260600</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7666,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7758,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-722000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1340000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2910000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-831000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-964000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1886000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1788000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-521000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2096000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
         <v>-759000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-478000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1521000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2546000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-519000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-613000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-447000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W94" s="3">
         <v>1026000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1093000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1321000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2039500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1085400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-807000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-445400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8485600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>301700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,97 +7886,101 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>247000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>249000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>500000</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>237000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>238000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>481000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>750000</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>761000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>92500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-906000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-729000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-170000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-537000</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>96000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-52000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-358000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-116000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-412000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-386500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-260300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-161600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-275800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-135000</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8068,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8160,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,271 +8252,283 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>572000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1723000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2331000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1153000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1141000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-42000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-629000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-339000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-176000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
         <v>649000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1555000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-514500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3305000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2368000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4992000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5279000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W100" s="3">
         <v>-544000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-456000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1337000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-311000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>667900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1901700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-859400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2637800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2125800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>610400</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-123000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>65000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>12000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-97000</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3">
         <v>-74000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>24000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>68000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>1000</v>
       </c>
       <c r="M101" s="3">
         <v>1000</v>
       </c>
       <c r="N101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O101" s="3">
         <v>-116500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-95000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-297000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-107000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>308000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>30000</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V101" s="3">
+      <c r="V101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W101" s="3">
         <v>-11000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>178000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>8000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-81300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-103000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>63700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-33700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>170200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>132600</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-814000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-141000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1412000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-476000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-407000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>679000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-866000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>637000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3081000</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>1447000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-375000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-445000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1938000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1429000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2367000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5870000</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W102" s="3">
         <v>-1158000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>525000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-287000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>245200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-574800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-75800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1261100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3052900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2281900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2522500</v>
       </c>
     </row>
